--- a/mafra.xlsx
+++ b/mafra.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\works\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\works\anti\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20656E3A-D88F-47BA-928D-0CE1629E301F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9CCCB4EB-AF34-47DA-8184-89E6FB8C437E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15796" tabRatio="728" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,8 +16,8 @@
     <sheet name="인증 평가표" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'인증 평가표'!$A$87:$G$94</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'인증 평가표'!$A$1:$G$104</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'인증 평가표'!$A$84:$G$90</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'인증 평가표'!$A$1:$G$99</definedName>
   </definedNames>
   <calcPr calcId="191029" iterateDelta="0"/>
   <extLst>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="289" uniqueCount="238">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="269" uniqueCount="234">
   <si>
     <t>□ 일반기준</t>
   </si>
@@ -51,9 +51,6 @@
     <t>평가 기준</t>
   </si>
   <si>
-    <t>평가결과</t>
-  </si>
-  <si>
     <t>일반기준</t>
   </si>
   <si>
@@ -127,9 +124,6 @@
   </si>
   <si>
     <t>HACCP</t>
-  </si>
-  <si>
-    <t>배점</t>
   </si>
   <si>
     <t>평과결과</t>
@@ -178,9 +172,6 @@
     <t>겨울에도 급수가 항시 가능하도록 대책이 마련되어 있는가?</t>
   </si>
   <si>
-    <t>배점/적합(Y) 여부</t>
-  </si>
-  <si>
     <t>0～5</t>
   </si>
   <si>
@@ -192,10 +183,6 @@
   </si>
   <si>
     <t xml:space="preserve">기록의 보관 상태가 양호하며 기록의무사항이 성실하게 작성되어 있는가? </t>
-  </si>
-  <si>
-    <t>배점/적합(Y) 여부</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>질병예방
@@ -1648,7 +1635,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="103">
+  <borders count="96">
     <border>
       <left/>
       <right/>
@@ -1888,51 +1875,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="medium">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="medium">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="medium">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="medium">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="medium">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color rgb="FF000000"/>
       </left>
@@ -2018,43 +1960,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right/>
-      <top style="medium">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="medium">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="medium">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="medium">
         <color rgb="FF000000"/>
       </left>
@@ -2107,19 +2012,6 @@
       <right/>
       <top/>
       <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color rgb="FF000000"/>
-      </left>
-      <right/>
-      <top style="medium">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="double">
         <color rgb="FF000000"/>
       </bottom>
       <diagonal/>
@@ -2964,7 +2856,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="219">
+  <cellXfs count="208">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2977,15 +2869,6 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2995,160 +2878,157 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="55" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="58" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="60" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="10" fillId="2" borderId="62" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="63" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="62" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="65" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="67" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="10" fillId="2" borderId="69" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="70" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="72" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="20" fontId="5" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="78" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="60" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="79" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="20" fontId="5" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="63" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="82" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="84" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="85" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="67" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="70" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="89" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="91" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="92" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="93" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="94" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="90" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="86" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="87" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="83" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -3166,78 +3046,72 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="66" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="73" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="54" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="80" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="5" fillId="2" borderId="48" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="72" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="5" fillId="2" borderId="41" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="65" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -3246,58 +3120,334 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="96" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="89" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="88" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="79" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="80" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="95" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="79" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="70" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="71" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="92" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="93" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="94" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="10" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="10" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="61" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="62" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="80" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="64" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="87" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="67" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="68" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="69" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="90" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="91" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="66" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="81" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="57" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="77" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="74" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="75" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="76" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="86" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -3312,317 +3462,26 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="93" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="61" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="66" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="63" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="64" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="68" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="69" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="81" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="82" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="83" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="88" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="63" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="64" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="84" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="73" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="54" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="59" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="57" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="74" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="75" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="76" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="77" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="78" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="10" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="10" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="58" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="71" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="59" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="57" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="97" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="98" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="99" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="100" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="101" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="86" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="87" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="102" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="86" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="61" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="62" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="5">
@@ -3658,13 +3517,13 @@
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>104775</xdr:colOff>
-      <xdr:row>63</xdr:row>
+      <xdr:row>60</xdr:row>
       <xdr:rowOff>409574</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>4</xdr:col>
       <xdr:colOff>1753878</xdr:colOff>
-      <xdr:row>63</xdr:row>
+      <xdr:row>60</xdr:row>
       <xdr:rowOff>1543049</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -3998,7 +3857,7 @@
     <tabColor rgb="FFFFC000"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:H119"/>
+  <dimension ref="A1:H114"/>
   <sheetFormatPr defaultRowHeight="16.899999999999999" x14ac:dyDescent="0.6"/>
   <cols>
     <col min="1" max="1" width="15.625" customWidth="1"/>
@@ -4014,1773 +3873,1679 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="17.25" thickBot="1" x14ac:dyDescent="0.65">
-      <c r="A2" s="4" t="s">
+    <row r="2" spans="1:8" ht="34.15" customHeight="1" thickTop="1" x14ac:dyDescent="0.6">
+      <c r="A2" s="145" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="103"/>
+      <c r="C2" s="148" t="s">
+        <v>72</v>
+      </c>
+      <c r="D2" s="149"/>
+      <c r="E2" s="150"/>
+      <c r="F2" s="78" t="s">
+        <v>49</v>
+      </c>
+      <c r="G2" s="71"/>
+      <c r="H2" s="2"/>
+    </row>
+    <row r="3" spans="1:8" ht="33.75" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="A3" s="146"/>
+      <c r="B3" s="104"/>
+      <c r="C3" s="112" t="s">
+        <v>40</v>
+      </c>
+      <c r="D3" s="113"/>
+      <c r="E3" s="151"/>
+      <c r="F3" s="79" t="s">
+        <v>49</v>
+      </c>
+      <c r="G3" s="80"/>
+    </row>
+    <row r="4" spans="1:8" ht="50.25" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="A4" s="146"/>
+      <c r="B4" s="104"/>
+      <c r="C4" s="112" t="s">
+        <v>211</v>
+      </c>
+      <c r="D4" s="113"/>
+      <c r="E4" s="151"/>
+      <c r="F4" s="79" t="s">
+        <v>71</v>
+      </c>
+      <c r="G4" s="80"/>
+      <c r="H4" s="2"/>
+    </row>
+    <row r="5" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="A5" s="146"/>
+      <c r="B5" s="104"/>
+      <c r="C5" s="115" t="s">
+        <v>61</v>
+      </c>
+      <c r="D5" s="115"/>
+      <c r="E5" s="130"/>
+      <c r="F5" s="154" t="s">
+        <v>50</v>
+      </c>
+      <c r="G5" s="143"/>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.6">
+      <c r="A6" s="146"/>
+      <c r="B6" s="104"/>
+      <c r="C6" s="38" t="s">
+        <v>60</v>
+      </c>
+      <c r="D6" s="83"/>
+      <c r="E6" s="84"/>
+      <c r="F6" s="155"/>
+      <c r="G6" s="144"/>
+    </row>
+    <row r="7" spans="1:8" ht="34.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.65">
+      <c r="A7" s="147"/>
+      <c r="B7" s="105"/>
+      <c r="C7" s="100" t="s">
+        <v>210</v>
+      </c>
+      <c r="D7" s="101"/>
+      <c r="E7" s="102"/>
+      <c r="F7" s="37" t="s">
+        <v>73</v>
+      </c>
+      <c r="G7" s="39"/>
+      <c r="H7" s="2"/>
+    </row>
+    <row r="9" spans="1:8" ht="19.899999999999999" thickBot="1" x14ac:dyDescent="0.65">
+      <c r="A9" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" ht="37.5" customHeight="1" thickTop="1" x14ac:dyDescent="0.6">
+      <c r="A10" s="122" t="s">
+        <v>86</v>
+      </c>
+      <c r="B10" s="133" t="s">
+        <v>6</v>
+      </c>
+      <c r="C10" s="159" t="s">
+        <v>46</v>
+      </c>
+      <c r="D10" s="160"/>
+      <c r="E10" s="160"/>
+      <c r="F10" s="7">
+        <v>10</v>
+      </c>
+      <c r="G10" s="8"/>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.6">
+      <c r="A11" s="122"/>
+      <c r="B11" s="133"/>
+      <c r="C11" s="131" t="s">
+        <v>41</v>
+      </c>
+      <c r="D11" s="132"/>
+      <c r="E11" s="132"/>
+      <c r="F11" s="9">
         <v>1</v>
       </c>
-      <c r="B2" s="188" t="s">
+      <c r="G11" s="10"/>
+      <c r="H11" s="2"/>
+    </row>
+    <row r="12" spans="1:8" ht="37.5" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="A12" s="122"/>
+      <c r="B12" s="133"/>
+      <c r="C12" s="131" t="s">
+        <v>74</v>
+      </c>
+      <c r="D12" s="132"/>
+      <c r="E12" s="132"/>
+      <c r="F12" s="9">
+        <v>1</v>
+      </c>
+      <c r="G12" s="10"/>
+    </row>
+    <row r="13" spans="1:8" ht="37.5" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="A13" s="122"/>
+      <c r="B13" s="133"/>
+      <c r="C13" s="131" t="s">
+        <v>75</v>
+      </c>
+      <c r="D13" s="132"/>
+      <c r="E13" s="132"/>
+      <c r="F13" s="9">
+        <v>1</v>
+      </c>
+      <c r="G13" s="10"/>
+    </row>
+    <row r="14" spans="1:8" ht="37.5" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="A14" s="122"/>
+      <c r="B14" s="133"/>
+      <c r="C14" s="131" t="s">
+        <v>76</v>
+      </c>
+      <c r="D14" s="132"/>
+      <c r="E14" s="132"/>
+      <c r="F14" s="9">
+        <v>1</v>
+      </c>
+      <c r="G14" s="10"/>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.6">
+      <c r="A15" s="122"/>
+      <c r="B15" s="133"/>
+      <c r="C15" s="131" t="s">
+        <v>77</v>
+      </c>
+      <c r="D15" s="132"/>
+      <c r="E15" s="132"/>
+      <c r="F15" s="9">
+        <v>1</v>
+      </c>
+      <c r="G15" s="10"/>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.6">
+      <c r="A16" s="122"/>
+      <c r="B16" s="133"/>
+      <c r="C16" s="131" t="s">
+        <v>78</v>
+      </c>
+      <c r="D16" s="132"/>
+      <c r="E16" s="132"/>
+      <c r="F16" s="9">
+        <v>1</v>
+      </c>
+      <c r="G16" s="10"/>
+      <c r="H16" s="2"/>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.6">
+      <c r="A17" s="122"/>
+      <c r="B17" s="133"/>
+      <c r="C17" s="131" t="s">
+        <v>79</v>
+      </c>
+      <c r="D17" s="132"/>
+      <c r="E17" s="132"/>
+      <c r="F17" s="9">
+        <v>1</v>
+      </c>
+      <c r="G17" s="10"/>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.6">
+      <c r="A18" s="122"/>
+      <c r="B18" s="133"/>
+      <c r="C18" s="131" t="s">
+        <v>80</v>
+      </c>
+      <c r="D18" s="132"/>
+      <c r="E18" s="132"/>
+      <c r="F18" s="9">
+        <v>1</v>
+      </c>
+      <c r="G18" s="10"/>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.6">
+      <c r="A19" s="122"/>
+      <c r="B19" s="133"/>
+      <c r="C19" s="131" t="s">
+        <v>81</v>
+      </c>
+      <c r="D19" s="132"/>
+      <c r="E19" s="132"/>
+      <c r="F19" s="9">
+        <v>1</v>
+      </c>
+      <c r="G19" s="10"/>
+      <c r="H19" s="2"/>
+    </row>
+    <row r="20" spans="1:8" ht="37.5" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="A20" s="122"/>
+      <c r="B20" s="127"/>
+      <c r="C20" s="156" t="s">
+        <v>82</v>
+      </c>
+      <c r="D20" s="157"/>
+      <c r="E20" s="157"/>
+      <c r="F20" s="11">
+        <v>1</v>
+      </c>
+      <c r="G20" s="4"/>
+    </row>
+    <row r="21" spans="1:8" ht="50.65" x14ac:dyDescent="0.6">
+      <c r="A21" s="122"/>
+      <c r="B21" s="34" t="s">
+        <v>7</v>
+      </c>
+      <c r="C21" s="134" t="s">
+        <v>201</v>
+      </c>
+      <c r="D21" s="135"/>
+      <c r="E21" s="135"/>
+      <c r="F21" s="27" t="s">
+        <v>52</v>
+      </c>
+      <c r="G21" s="32"/>
+      <c r="H21" s="2"/>
+    </row>
+    <row r="22" spans="1:8" ht="33.75" x14ac:dyDescent="0.6">
+      <c r="A22" s="122"/>
+      <c r="B22" s="16" t="s">
+        <v>83</v>
+      </c>
+      <c r="C22" s="134" t="s">
+        <v>84</v>
+      </c>
+      <c r="D22" s="135"/>
+      <c r="E22" s="135"/>
+      <c r="F22" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="G22" s="6"/>
+      <c r="H22" s="2"/>
+    </row>
+    <row r="23" spans="1:8" ht="33.75" x14ac:dyDescent="0.6">
+      <c r="A23" s="121" t="s">
+        <v>88</v>
+      </c>
+      <c r="B23" s="16" t="s">
+        <v>8</v>
+      </c>
+      <c r="C23" s="114" t="s">
+        <v>202</v>
+      </c>
+      <c r="D23" s="115"/>
+      <c r="E23" s="115"/>
+      <c r="F23" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="G23" s="17"/>
+      <c r="H23" s="2"/>
+    </row>
+    <row r="24" spans="1:8" ht="51.75" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="A24" s="122"/>
+      <c r="B24" s="16" t="s">
+        <v>6</v>
+      </c>
+      <c r="C24" s="134" t="s">
+        <v>87</v>
+      </c>
+      <c r="D24" s="135"/>
+      <c r="E24" s="135"/>
+      <c r="F24" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="G24" s="67"/>
+      <c r="H24" s="2"/>
+    </row>
+    <row r="25" spans="1:8" ht="33.75" x14ac:dyDescent="0.6">
+      <c r="A25" s="122"/>
+      <c r="B25" s="16" t="s">
+        <v>9</v>
+      </c>
+      <c r="C25" s="114" t="s">
+        <v>196</v>
+      </c>
+      <c r="D25" s="115"/>
+      <c r="E25" s="115"/>
+      <c r="F25" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="G25" s="17"/>
+    </row>
+    <row r="26" spans="1:8" ht="105.75" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="A26" s="121" t="s">
+        <v>95</v>
+      </c>
+      <c r="B26" s="126" t="s">
+        <v>47</v>
+      </c>
+      <c r="C26" s="114" t="s">
+        <v>203</v>
+      </c>
+      <c r="D26" s="115"/>
+      <c r="E26" s="130"/>
+      <c r="F26" s="138" t="s">
+        <v>56</v>
+      </c>
+      <c r="G26" s="152"/>
+      <c r="H26" s="2"/>
+    </row>
+    <row r="27" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="A27" s="122"/>
+      <c r="B27" s="127"/>
+      <c r="C27" s="58" t="s">
+        <v>194</v>
+      </c>
+      <c r="D27" s="59"/>
+      <c r="E27" s="60" t="s">
+        <v>209</v>
+      </c>
+      <c r="F27" s="139"/>
+      <c r="G27" s="153"/>
+    </row>
+    <row r="28" spans="1:8" ht="33.75" x14ac:dyDescent="0.6">
+      <c r="A28" s="122"/>
+      <c r="B28" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="C28" s="114" t="s">
+        <v>89</v>
+      </c>
+      <c r="D28" s="115"/>
+      <c r="E28" s="115"/>
+      <c r="F28" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="G28" s="17"/>
+      <c r="H28" s="2"/>
+    </row>
+    <row r="29" spans="1:8" ht="33.75" x14ac:dyDescent="0.6">
+      <c r="A29" s="122"/>
+      <c r="B29" s="31" t="s">
+        <v>11</v>
+      </c>
+      <c r="C29" s="140" t="s">
+        <v>90</v>
+      </c>
+      <c r="D29" s="141"/>
+      <c r="E29" s="141"/>
+      <c r="F29" s="36" t="s">
+        <v>91</v>
+      </c>
+      <c r="G29" s="32"/>
+    </row>
+    <row r="30" spans="1:8" ht="67.5" x14ac:dyDescent="0.6">
+      <c r="A30" s="158"/>
+      <c r="B30" s="18" t="s">
+        <v>92</v>
+      </c>
+      <c r="C30" s="140" t="s">
+        <v>93</v>
+      </c>
+      <c r="D30" s="141"/>
+      <c r="E30" s="141"/>
+      <c r="F30" s="19" t="s">
+        <v>94</v>
+      </c>
+      <c r="G30" s="6"/>
+      <c r="H30" s="2"/>
+    </row>
+    <row r="31" spans="1:8" ht="118.15" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="A31" s="77" t="s">
+        <v>96</v>
+      </c>
+      <c r="B31" s="85"/>
+      <c r="C31" s="140" t="s">
+        <v>97</v>
+      </c>
+      <c r="D31" s="141"/>
+      <c r="E31" s="142"/>
+      <c r="F31" s="79" t="s">
+        <v>98</v>
+      </c>
+      <c r="G31" s="80"/>
+    </row>
+    <row r="32" spans="1:8" ht="50.65" x14ac:dyDescent="0.6">
+      <c r="A32" s="122" t="s">
+        <v>99</v>
+      </c>
+      <c r="B32" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="C32" s="131" t="s">
+        <v>51</v>
+      </c>
+      <c r="D32" s="132"/>
+      <c r="E32" s="132"/>
+      <c r="F32" s="13" t="s">
+        <v>100</v>
+      </c>
+      <c r="G32" s="10"/>
+    </row>
+    <row r="33" spans="1:8" ht="33.75" x14ac:dyDescent="0.6">
+      <c r="A33" s="122"/>
+      <c r="B33" s="16" t="s">
+        <v>101</v>
+      </c>
+      <c r="C33" s="134" t="s">
+        <v>215</v>
+      </c>
+      <c r="D33" s="135"/>
+      <c r="E33" s="135"/>
+      <c r="F33" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="G33" s="70"/>
+    </row>
+    <row r="34" spans="1:8" ht="33.75" x14ac:dyDescent="0.6">
+      <c r="A34" s="122"/>
+      <c r="B34" s="16" t="s">
+        <v>36</v>
+      </c>
+      <c r="C34" s="114" t="s">
+        <v>37</v>
+      </c>
+      <c r="D34" s="115"/>
+      <c r="E34" s="115"/>
+      <c r="F34" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="G34" s="17"/>
+    </row>
+    <row r="35" spans="1:8" ht="50.65" x14ac:dyDescent="0.6">
+      <c r="A35" s="122"/>
+      <c r="B35" s="126" t="s">
+        <v>13</v>
+      </c>
+      <c r="C35" s="134" t="s">
+        <v>216</v>
+      </c>
+      <c r="D35" s="135"/>
+      <c r="E35" s="135"/>
+      <c r="F35" s="27" t="s">
+        <v>103</v>
+      </c>
+      <c r="G35" s="29"/>
+    </row>
+    <row r="36" spans="1:8" ht="57" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="A36" s="122"/>
+      <c r="B36" s="133"/>
+      <c r="C36" s="136" t="s">
+        <v>217</v>
+      </c>
+      <c r="D36" s="137"/>
+      <c r="E36" s="137"/>
+      <c r="F36" s="27" t="s">
+        <v>64</v>
+      </c>
+      <c r="G36" s="67"/>
+      <c r="H36" s="2"/>
+    </row>
+    <row r="37" spans="1:8" ht="67.5" x14ac:dyDescent="0.6">
+      <c r="A37" s="162" t="s">
+        <v>105</v>
+      </c>
+      <c r="B37" s="18" t="s">
+        <v>14</v>
+      </c>
+      <c r="C37" s="135" t="s">
+        <v>106</v>
+      </c>
+      <c r="D37" s="135"/>
+      <c r="E37" s="135"/>
+      <c r="F37" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="G37" s="6"/>
+    </row>
+    <row r="38" spans="1:8" ht="41.25" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="A38" s="162"/>
+      <c r="B38" s="163" t="s">
+        <v>15</v>
+      </c>
+      <c r="C38" s="164" t="s">
+        <v>197</v>
+      </c>
+      <c r="D38" s="164"/>
+      <c r="E38" s="164"/>
+      <c r="F38" s="181" t="s">
+        <v>62</v>
+      </c>
+      <c r="G38" s="175"/>
+    </row>
+    <row r="39" spans="1:8" ht="32.25" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="A39" s="162"/>
+      <c r="B39" s="163"/>
+      <c r="C39" s="86" t="s">
+        <v>108</v>
+      </c>
+      <c r="D39" s="108"/>
+      <c r="E39" s="109"/>
+      <c r="F39" s="182"/>
+      <c r="G39" s="175"/>
+    </row>
+    <row r="40" spans="1:8" ht="23.25" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="A40" s="162"/>
+      <c r="B40" s="176" t="s">
+        <v>16</v>
+      </c>
+      <c r="C40" s="135" t="s">
+        <v>42</v>
+      </c>
+      <c r="D40" s="135"/>
+      <c r="E40" s="135"/>
+      <c r="F40" s="138" t="s">
+        <v>63</v>
+      </c>
+      <c r="G40" s="143"/>
+    </row>
+    <row r="41" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="A41" s="162"/>
+      <c r="B41" s="176"/>
+      <c r="C41" s="61" t="s">
+        <v>109</v>
+      </c>
+      <c r="D41" s="183"/>
+      <c r="E41" s="184"/>
+      <c r="F41" s="139"/>
+      <c r="G41" s="143"/>
+    </row>
+    <row r="42" spans="1:8" ht="53.25" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="A42" s="162"/>
+      <c r="B42" s="31" t="s">
+        <v>110</v>
+      </c>
+      <c r="C42" s="136" t="s">
+        <v>204</v>
+      </c>
+      <c r="D42" s="137"/>
+      <c r="E42" s="180"/>
+      <c r="F42" s="27" t="s">
+        <v>64</v>
+      </c>
+      <c r="G42" s="29"/>
+      <c r="H42" s="2"/>
+    </row>
+    <row r="43" spans="1:8" ht="158.25" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="A43" s="177" t="s">
+        <v>111</v>
+      </c>
+      <c r="B43" s="33" t="s">
+        <v>112</v>
+      </c>
+      <c r="C43" s="165" t="s">
+        <v>198</v>
+      </c>
+      <c r="D43" s="166"/>
+      <c r="E43" s="167"/>
+      <c r="F43" s="35" t="s">
+        <v>113</v>
+      </c>
+      <c r="G43" s="29"/>
+    </row>
+    <row r="44" spans="1:8" ht="33.75" x14ac:dyDescent="0.6">
+      <c r="A44" s="178"/>
+      <c r="B44" s="33" t="s">
+        <v>114</v>
+      </c>
+      <c r="C44" s="165" t="s">
+        <v>121</v>
+      </c>
+      <c r="D44" s="166"/>
+      <c r="E44" s="167"/>
+      <c r="F44" s="35" t="s">
+        <v>122</v>
+      </c>
+      <c r="G44" s="29"/>
+    </row>
+    <row r="45" spans="1:8" ht="33.75" x14ac:dyDescent="0.6">
+      <c r="A45" s="178"/>
+      <c r="B45" s="33" t="s">
+        <v>115</v>
+      </c>
+      <c r="C45" s="165" t="s">
+        <v>218</v>
+      </c>
+      <c r="D45" s="166"/>
+      <c r="E45" s="167"/>
+      <c r="F45" s="35" t="s">
+        <v>123</v>
+      </c>
+      <c r="G45" s="29"/>
+    </row>
+    <row r="46" spans="1:8" ht="33.75" x14ac:dyDescent="0.6">
+      <c r="A46" s="178"/>
+      <c r="B46" s="33" t="s">
+        <v>116</v>
+      </c>
+      <c r="C46" s="165" t="s">
+        <v>124</v>
+      </c>
+      <c r="D46" s="166"/>
+      <c r="E46" s="167"/>
+      <c r="F46" s="35" t="s">
+        <v>125</v>
+      </c>
+      <c r="G46" s="29"/>
+    </row>
+    <row r="47" spans="1:8" ht="33.75" x14ac:dyDescent="0.6">
+      <c r="A47" s="178"/>
+      <c r="B47" s="33" t="s">
+        <v>117</v>
+      </c>
+      <c r="C47" s="165" t="s">
+        <v>126</v>
+      </c>
+      <c r="D47" s="166"/>
+      <c r="E47" s="167"/>
+      <c r="F47" s="35" t="s">
+        <v>127</v>
+      </c>
+      <c r="G47" s="29"/>
+    </row>
+    <row r="48" spans="1:8" ht="33.75" x14ac:dyDescent="0.6">
+      <c r="A48" s="179"/>
+      <c r="B48" s="33" t="s">
+        <v>118</v>
+      </c>
+      <c r="C48" s="165" t="s">
+        <v>128</v>
+      </c>
+      <c r="D48" s="166"/>
+      <c r="E48" s="167"/>
+      <c r="F48" s="35" t="s">
+        <v>129</v>
+      </c>
+      <c r="G48" s="29"/>
+    </row>
+    <row r="49" spans="1:8" ht="34.15" thickBot="1" x14ac:dyDescent="0.65">
+      <c r="A49" s="185" t="s">
+        <v>119</v>
+      </c>
+      <c r="B49" s="186"/>
+      <c r="C49" s="187" t="s">
+        <v>120</v>
+      </c>
+      <c r="D49" s="187"/>
+      <c r="E49" s="188"/>
+      <c r="F49" s="14" t="s">
+        <v>176</v>
+      </c>
+      <c r="G49" s="15"/>
+      <c r="H49" s="2"/>
+    </row>
+    <row r="51" spans="1:8" ht="19.899999999999999" thickBot="1" x14ac:dyDescent="0.65">
+      <c r="A51" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="52" spans="1:8" ht="17.25" thickTop="1" x14ac:dyDescent="0.6">
+      <c r="A52" s="122" t="s">
+        <v>132</v>
+      </c>
+      <c r="B52" s="189" t="s">
+        <v>18</v>
+      </c>
+      <c r="C52" s="156" t="s">
+        <v>130</v>
+      </c>
+      <c r="D52" s="157"/>
+      <c r="E52" s="157"/>
+      <c r="F52" s="11" t="s">
+        <v>43</v>
+      </c>
+      <c r="G52" s="4"/>
+    </row>
+    <row r="53" spans="1:8" ht="53.25" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="A53" s="122"/>
+      <c r="B53" s="133"/>
+      <c r="C53" s="140" t="s">
+        <v>195</v>
+      </c>
+      <c r="D53" s="141"/>
+      <c r="E53" s="141"/>
+      <c r="F53" s="18" t="s">
+        <v>43</v>
+      </c>
+      <c r="G53" s="72"/>
+    </row>
+    <row r="54" spans="1:8" x14ac:dyDescent="0.6">
+      <c r="A54" s="122"/>
+      <c r="B54" s="133"/>
+      <c r="C54" s="140" t="s">
+        <v>44</v>
+      </c>
+      <c r="D54" s="141"/>
+      <c r="E54" s="141"/>
+      <c r="F54" s="18" t="s">
+        <v>43</v>
+      </c>
+      <c r="G54" s="4"/>
+    </row>
+    <row r="55" spans="1:8" ht="33.75" x14ac:dyDescent="0.6">
+      <c r="A55" s="122"/>
+      <c r="B55" s="133"/>
+      <c r="C55" s="134" t="s">
+        <v>205</v>
+      </c>
+      <c r="D55" s="135"/>
+      <c r="E55" s="135"/>
+      <c r="F55" s="5" t="s">
+        <v>131</v>
+      </c>
+      <c r="G55" s="6"/>
+    </row>
+    <row r="56" spans="1:8" ht="102.75" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="A56" s="122"/>
+      <c r="B56" s="133"/>
+      <c r="C56" s="134" t="s">
+        <v>133</v>
+      </c>
+      <c r="D56" s="135"/>
+      <c r="E56" s="168"/>
+      <c r="F56" s="27" t="s">
+        <v>48</v>
+      </c>
+      <c r="G56" s="29"/>
+    </row>
+    <row r="57" spans="1:8" ht="84" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="A57" s="122"/>
+      <c r="B57" s="133"/>
+      <c r="C57" s="134" t="s">
+        <v>135</v>
+      </c>
+      <c r="D57" s="135"/>
+      <c r="E57" s="168"/>
+      <c r="F57" s="27" t="s">
+        <v>136</v>
+      </c>
+      <c r="G57" s="67"/>
+    </row>
+    <row r="58" spans="1:8" ht="118.15" x14ac:dyDescent="0.6">
+      <c r="A58" s="122"/>
+      <c r="B58" s="133"/>
+      <c r="C58" s="119" t="s">
+        <v>137</v>
+      </c>
+      <c r="D58" s="120"/>
+      <c r="E58" s="190"/>
+      <c r="F58" s="40" t="s">
+        <v>138</v>
+      </c>
+      <c r="G58" s="29"/>
+      <c r="H58" s="2"/>
+    </row>
+    <row r="59" spans="1:8" ht="33.75" x14ac:dyDescent="0.6">
+      <c r="A59" s="122"/>
+      <c r="B59" s="133"/>
+      <c r="C59" s="134" t="s">
+        <v>139</v>
+      </c>
+      <c r="D59" s="135"/>
+      <c r="E59" s="168"/>
+      <c r="F59" s="27" t="s">
+        <v>140</v>
+      </c>
+      <c r="G59" s="29"/>
+    </row>
+    <row r="60" spans="1:8" ht="102" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="A60" s="122"/>
+      <c r="B60" s="16" t="s">
+        <v>141</v>
+      </c>
+      <c r="C60" s="169" t="s">
+        <v>142</v>
+      </c>
+      <c r="D60" s="170"/>
+      <c r="E60" s="170"/>
+      <c r="F60" s="64" t="s">
+        <v>144</v>
+      </c>
+      <c r="G60" s="6"/>
+    </row>
+    <row r="61" spans="1:8" ht="166.5" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="A61" s="81" t="s">
+        <v>145</v>
+      </c>
+      <c r="B61" s="76"/>
+      <c r="C61" s="119" t="s">
+        <v>199</v>
+      </c>
+      <c r="D61" s="120"/>
+      <c r="E61" s="120"/>
+      <c r="F61" s="27" t="s">
+        <v>134</v>
+      </c>
+      <c r="G61" s="66"/>
+      <c r="H61" s="2"/>
+    </row>
+    <row r="62" spans="1:8" ht="101.25" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="A62" s="81" t="s">
+        <v>146</v>
+      </c>
+      <c r="B62" s="76"/>
+      <c r="C62" s="119" t="s">
+        <v>150</v>
+      </c>
+      <c r="D62" s="120"/>
+      <c r="E62" s="120"/>
+      <c r="F62" s="27" t="s">
+        <v>151</v>
+      </c>
+      <c r="G62" s="32"/>
+    </row>
+    <row r="63" spans="1:8" ht="108" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="A63" s="106" t="s">
+        <v>147</v>
+      </c>
+      <c r="B63" s="76"/>
+      <c r="C63" s="134" t="s">
+        <v>148</v>
+      </c>
+      <c r="D63" s="135"/>
+      <c r="E63" s="135"/>
+      <c r="F63" s="64" t="s">
+        <v>152</v>
+      </c>
+      <c r="G63" s="32"/>
+    </row>
+    <row r="64" spans="1:8" x14ac:dyDescent="0.6">
+      <c r="A64" s="107"/>
+      <c r="B64" s="76"/>
+      <c r="C64" s="112" t="s">
+        <v>149</v>
+      </c>
+      <c r="D64" s="113"/>
+      <c r="E64" s="151"/>
+      <c r="F64" s="64" t="s">
+        <v>143</v>
+      </c>
+      <c r="G64" s="29"/>
+    </row>
+    <row r="65" spans="1:7" ht="328.5" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="A65" s="82" t="s">
+        <v>153</v>
+      </c>
+      <c r="B65" s="76"/>
+      <c r="C65" s="134" t="s">
+        <v>155</v>
+      </c>
+      <c r="D65" s="135"/>
+      <c r="E65" s="135"/>
+      <c r="F65" s="27" t="s">
+        <v>104</v>
+      </c>
+      <c r="G65" s="32"/>
+    </row>
+    <row r="66" spans="1:7" ht="51.75" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="A66" s="121" t="s">
+        <v>154</v>
+      </c>
+      <c r="B66" s="34" t="s">
+        <v>19</v>
+      </c>
+      <c r="C66" s="123" t="s">
+        <v>219</v>
+      </c>
+      <c r="D66" s="124"/>
+      <c r="E66" s="125"/>
+      <c r="F66" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="G66" s="17"/>
+    </row>
+    <row r="67" spans="1:7" ht="33.75" x14ac:dyDescent="0.6">
+      <c r="A67" s="122"/>
+      <c r="B67" s="126" t="s">
+        <v>32</v>
+      </c>
+      <c r="C67" s="128" t="s">
+        <v>220</v>
+      </c>
+      <c r="D67" s="129"/>
+      <c r="E67" s="129"/>
+      <c r="F67" s="62" t="s">
+        <v>157</v>
+      </c>
+      <c r="G67" s="65"/>
+    </row>
+    <row r="68" spans="1:7" x14ac:dyDescent="0.6">
+      <c r="A68" s="122"/>
+      <c r="B68" s="127"/>
+      <c r="C68" s="140" t="s">
+        <v>156</v>
+      </c>
+      <c r="D68" s="141"/>
+      <c r="E68" s="171"/>
+      <c r="F68" s="20" t="s">
+        <v>43</v>
+      </c>
+      <c r="G68" s="12"/>
+    </row>
+    <row r="69" spans="1:7" ht="33.75" x14ac:dyDescent="0.6">
+      <c r="A69" s="122"/>
+      <c r="B69" s="126" t="s">
+        <v>20</v>
+      </c>
+      <c r="C69" s="128" t="s">
+        <v>158</v>
+      </c>
+      <c r="D69" s="129"/>
+      <c r="E69" s="129"/>
+      <c r="F69" s="63" t="s">
+        <v>159</v>
+      </c>
+      <c r="G69" s="65"/>
+    </row>
+    <row r="70" spans="1:7" ht="33.75" x14ac:dyDescent="0.6">
+      <c r="A70" s="122"/>
+      <c r="B70" s="127"/>
+      <c r="C70" s="172" t="s">
+        <v>160</v>
+      </c>
+      <c r="D70" s="173"/>
+      <c r="E70" s="174"/>
+      <c r="F70" s="28" t="s">
+        <v>161</v>
+      </c>
+      <c r="G70" s="30"/>
+    </row>
+    <row r="71" spans="1:7" ht="33.75" x14ac:dyDescent="0.6">
+      <c r="A71" s="122"/>
+      <c r="B71" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="C71" s="134" t="s">
+        <v>162</v>
+      </c>
+      <c r="D71" s="135"/>
+      <c r="E71" s="135"/>
+      <c r="F71" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="G71" s="6"/>
+    </row>
+    <row r="72" spans="1:7" ht="33.75" x14ac:dyDescent="0.6">
+      <c r="A72" s="121" t="s">
+        <v>163</v>
+      </c>
+      <c r="B72" s="16" t="s">
+        <v>8</v>
+      </c>
+      <c r="C72" s="134" t="s">
+        <v>164</v>
+      </c>
+      <c r="D72" s="135"/>
+      <c r="E72" s="135"/>
+      <c r="F72" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="G72" s="6"/>
+    </row>
+    <row r="73" spans="1:7" ht="33.75" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="A73" s="122"/>
+      <c r="B73" s="34" t="s">
+        <v>22</v>
+      </c>
+      <c r="C73" s="114" t="s">
+        <v>165</v>
+      </c>
+      <c r="D73" s="115"/>
+      <c r="E73" s="115"/>
+      <c r="F73" s="27" t="s">
+        <v>58</v>
+      </c>
+      <c r="G73" s="32"/>
+    </row>
+    <row r="74" spans="1:7" ht="33.75" x14ac:dyDescent="0.6">
+      <c r="A74" s="122"/>
+      <c r="B74" s="126" t="s">
+        <v>23</v>
+      </c>
+      <c r="C74" s="134" t="s">
+        <v>166</v>
+      </c>
+      <c r="D74" s="135"/>
+      <c r="E74" s="135"/>
+      <c r="F74" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="G74" s="6"/>
+    </row>
+    <row r="75" spans="1:7" ht="37.5" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="A75" s="122"/>
+      <c r="B75" s="133"/>
+      <c r="C75" s="114" t="s">
+        <v>206</v>
+      </c>
+      <c r="D75" s="115"/>
+      <c r="E75" s="130"/>
+      <c r="F75" s="27" t="s">
+        <v>68</v>
+      </c>
+      <c r="G75" s="29"/>
+    </row>
+    <row r="76" spans="1:7" ht="33.75" x14ac:dyDescent="0.6">
+      <c r="A76" s="122"/>
+      <c r="B76" s="126" t="s">
+        <v>24</v>
+      </c>
+      <c r="C76" s="134" t="s">
+        <v>167</v>
+      </c>
+      <c r="D76" s="135"/>
+      <c r="E76" s="135"/>
+      <c r="F76" s="19" t="s">
+        <v>58</v>
+      </c>
+      <c r="G76" s="6"/>
+    </row>
+    <row r="77" spans="1:7" ht="33.75" x14ac:dyDescent="0.6">
+      <c r="A77" s="161"/>
+      <c r="B77" s="133"/>
+      <c r="C77" s="134" t="s">
+        <v>200</v>
+      </c>
+      <c r="D77" s="135"/>
+      <c r="E77" s="135"/>
+      <c r="F77" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="G77" s="6"/>
+    </row>
+    <row r="78" spans="1:7" ht="33.75" x14ac:dyDescent="0.6">
+      <c r="A78" s="196" t="s">
+        <v>168</v>
+      </c>
+      <c r="B78" s="126" t="s">
+        <v>38</v>
+      </c>
+      <c r="C78" s="197" t="s">
+        <v>169</v>
+      </c>
+      <c r="D78" s="198"/>
+      <c r="E78" s="198"/>
+      <c r="F78" s="68" t="s">
+        <v>208</v>
+      </c>
+      <c r="G78" s="69"/>
+    </row>
+    <row r="79" spans="1:7" ht="33.75" x14ac:dyDescent="0.6">
+      <c r="A79" s="196"/>
+      <c r="B79" s="133"/>
+      <c r="C79" s="199" t="s">
+        <v>70</v>
+      </c>
+      <c r="D79" s="200"/>
+      <c r="E79" s="200"/>
+      <c r="F79" s="68" t="s">
+        <v>208</v>
+      </c>
+      <c r="G79" s="69"/>
+    </row>
+    <row r="80" spans="1:7" ht="33.75" x14ac:dyDescent="0.6">
+      <c r="A80" s="106" t="s">
+        <v>25</v>
+      </c>
+      <c r="B80" s="201"/>
+      <c r="C80" s="134" t="s">
+        <v>207</v>
+      </c>
+      <c r="D80" s="135"/>
+      <c r="E80" s="135"/>
+      <c r="F80" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="G80" s="21"/>
+    </row>
+    <row r="81" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="A81" s="202" t="s">
+        <v>33</v>
+      </c>
+      <c r="B81" s="22" t="s">
+        <v>26</v>
+      </c>
+      <c r="C81" s="204" t="s">
+        <v>213</v>
+      </c>
+      <c r="D81" s="205"/>
+      <c r="E81" s="205"/>
+      <c r="F81" s="22">
+        <v>3</v>
+      </c>
+      <c r="G81" s="23"/>
+    </row>
+    <row r="82" spans="1:8" ht="22.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.65">
+      <c r="A82" s="203"/>
+      <c r="B82" s="24" t="s">
+        <v>27</v>
+      </c>
+      <c r="C82" s="206" t="s">
+        <v>212</v>
+      </c>
+      <c r="D82" s="207"/>
+      <c r="E82" s="25"/>
+      <c r="F82" s="24">
         <v>2</v>
       </c>
-      <c r="C2" s="188"/>
-      <c r="D2" s="188"/>
-      <c r="E2" s="188"/>
-      <c r="F2" s="83" t="s">
-        <v>41</v>
-      </c>
-      <c r="G2" s="6" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" ht="34.15" customHeight="1" thickTop="1" x14ac:dyDescent="0.6">
-      <c r="A3" s="191" t="s">
+      <c r="G82" s="26"/>
+    </row>
+    <row r="83" spans="1:8" ht="17.25" thickTop="1" x14ac:dyDescent="0.6"/>
+    <row r="84" spans="1:8" ht="19.899999999999999" thickBot="1" x14ac:dyDescent="0.65">
+      <c r="A84" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="B84" s="1"/>
+    </row>
+    <row r="85" spans="1:8" ht="24" customHeight="1" thickTop="1" x14ac:dyDescent="0.6">
+      <c r="A85" s="98" t="s">
+        <v>29</v>
+      </c>
+      <c r="B85" s="89"/>
+      <c r="C85" s="110" t="s">
+        <v>34</v>
+      </c>
+      <c r="D85" s="111"/>
+      <c r="E85" s="111"/>
+      <c r="F85" s="11">
+        <v>5</v>
+      </c>
+      <c r="G85" s="4"/>
+    </row>
+    <row r="86" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="A86" s="82" t="s">
+        <v>171</v>
+      </c>
+      <c r="B86" s="90"/>
+      <c r="C86" s="112" t="s">
+        <v>172</v>
+      </c>
+      <c r="D86" s="113"/>
+      <c r="E86" s="113"/>
+      <c r="F86" s="18">
+        <v>5</v>
+      </c>
+      <c r="G86" s="4"/>
+    </row>
+    <row r="87" spans="1:8" ht="43.5" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="A87" s="82" t="s">
+        <v>45</v>
+      </c>
+      <c r="B87" s="90"/>
+      <c r="C87" s="112" t="s">
+        <v>173</v>
+      </c>
+      <c r="D87" s="113"/>
+      <c r="E87" s="113"/>
+      <c r="F87" s="18">
+        <v>5</v>
+      </c>
+      <c r="G87" s="4"/>
+    </row>
+    <row r="88" spans="1:8" ht="33.75" x14ac:dyDescent="0.6">
+      <c r="A88" s="82" t="s">
+        <v>30</v>
+      </c>
+      <c r="B88" s="90"/>
+      <c r="C88" s="112" t="s">
+        <v>35</v>
+      </c>
+      <c r="D88" s="113"/>
+      <c r="E88" s="113"/>
+      <c r="F88" s="31">
+        <v>5</v>
+      </c>
+      <c r="G88" s="29"/>
+    </row>
+    <row r="89" spans="1:8" ht="41.25" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="A89" s="82" t="s">
+        <v>31</v>
+      </c>
+      <c r="B89" s="90"/>
+      <c r="C89" s="114" t="s">
+        <v>174</v>
+      </c>
+      <c r="D89" s="115"/>
+      <c r="E89" s="115"/>
+      <c r="F89" s="34">
+        <v>5</v>
+      </c>
+      <c r="G89" s="41"/>
+    </row>
+    <row r="90" spans="1:8" ht="74.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.65">
+      <c r="A90" s="99" t="s">
+        <v>175</v>
+      </c>
+      <c r="B90" s="97"/>
+      <c r="C90" s="116" t="s">
+        <v>214</v>
+      </c>
+      <c r="D90" s="117"/>
+      <c r="E90" s="118"/>
+      <c r="F90" s="42">
+        <v>10</v>
+      </c>
+      <c r="G90" s="43"/>
+      <c r="H90" s="2"/>
+    </row>
+    <row r="91" spans="1:8" ht="17.25" thickTop="1" x14ac:dyDescent="0.6">
+      <c r="A91" s="2"/>
+      <c r="B91" s="2"/>
+      <c r="C91" s="2"/>
+      <c r="D91" s="2"/>
+      <c r="E91" s="2"/>
+      <c r="F91" s="2"/>
+      <c r="G91" s="2"/>
+    </row>
+    <row r="92" spans="1:8" ht="19.5" x14ac:dyDescent="0.6">
+      <c r="A92" s="1" t="s">
+        <v>221</v>
+      </c>
+      <c r="B92" s="1"/>
+    </row>
+    <row r="93" spans="1:8" ht="39" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="A93" s="93" t="s">
+        <v>222</v>
+      </c>
+      <c r="B93" s="94"/>
+      <c r="C93" s="110" t="s">
+        <v>228</v>
+      </c>
+      <c r="D93" s="111"/>
+      <c r="E93" s="111"/>
+      <c r="F93" s="73" t="s">
+        <v>64</v>
+      </c>
+      <c r="G93" s="74"/>
+    </row>
+    <row r="94" spans="1:8" ht="39" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="A94" s="95" t="s">
+        <v>223</v>
+      </c>
+      <c r="B94" s="90"/>
+      <c r="C94" s="112" t="s">
+        <v>229</v>
+      </c>
+      <c r="D94" s="113"/>
+      <c r="E94" s="113"/>
+      <c r="F94" s="73" t="s">
+        <v>64</v>
+      </c>
+      <c r="G94" s="74"/>
+    </row>
+    <row r="95" spans="1:8" ht="129.75" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="A95" s="95" t="s">
+        <v>224</v>
+      </c>
+      <c r="B95" s="90"/>
+      <c r="C95" s="112" t="s">
+        <v>230</v>
+      </c>
+      <c r="D95" s="113"/>
+      <c r="E95" s="113"/>
+      <c r="F95" s="73" t="s">
+        <v>64</v>
+      </c>
+      <c r="G95" s="74"/>
+    </row>
+    <row r="96" spans="1:8" ht="49.5" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="A96" s="95" t="s">
+        <v>225</v>
+      </c>
+      <c r="B96" s="90"/>
+      <c r="C96" s="112" t="s">
+        <v>231</v>
+      </c>
+      <c r="D96" s="113"/>
+      <c r="E96" s="151"/>
+      <c r="F96" s="73" t="s">
+        <v>64</v>
+      </c>
+      <c r="G96" s="75"/>
+    </row>
+    <row r="97" spans="1:8" ht="122.25" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="A97" s="95" t="s">
+        <v>226</v>
+      </c>
+      <c r="B97" s="90"/>
+      <c r="C97" s="112" t="s">
+        <v>192</v>
+      </c>
+      <c r="D97" s="113"/>
+      <c r="E97" s="151"/>
+      <c r="F97" s="73" t="s">
+        <v>64</v>
+      </c>
+      <c r="G97" s="30"/>
+    </row>
+    <row r="98" spans="1:8" ht="38.25" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="A98" s="92" t="s">
+        <v>227</v>
+      </c>
+      <c r="B98" s="91"/>
+      <c r="C98" s="114" t="s">
+        <v>232</v>
+      </c>
+      <c r="D98" s="115"/>
+      <c r="E98" s="115"/>
+      <c r="F98" s="73" t="s">
+        <v>64</v>
+      </c>
+      <c r="G98" s="41"/>
+    </row>
+    <row r="99" spans="1:8" ht="36.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.65">
+      <c r="A99" s="96" t="s">
+        <v>141</v>
+      </c>
+      <c r="B99" s="97"/>
+      <c r="C99" s="116" t="s">
+        <v>233</v>
+      </c>
+      <c r="D99" s="117"/>
+      <c r="E99" s="118"/>
+      <c r="F99" s="88" t="s">
+        <v>64</v>
+      </c>
+      <c r="G99" s="87"/>
+      <c r="H99" s="2"/>
+    </row>
+    <row r="100" spans="1:8" hidden="1" x14ac:dyDescent="0.6">
+      <c r="E100" s="3"/>
+    </row>
+    <row r="101" spans="1:8" hidden="1" x14ac:dyDescent="0.6"/>
+    <row r="102" spans="1:8" ht="19.5" hidden="1" x14ac:dyDescent="0.6">
+      <c r="A102" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="B102" s="1"/>
+      <c r="C102" s="1"/>
+      <c r="D102" s="1"/>
+      <c r="E102" s="1"/>
+      <c r="F102" s="1"/>
+      <c r="G102" s="1"/>
+    </row>
+    <row r="103" spans="1:8" ht="26.25" hidden="1" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="A103" s="49" t="s">
+        <v>1</v>
+      </c>
+      <c r="B103" s="193" t="s">
+        <v>2</v>
+      </c>
+      <c r="C103" s="193"/>
+      <c r="D103" s="193"/>
+      <c r="E103" s="193"/>
+      <c r="F103" s="50" t="s">
+        <v>39</v>
+      </c>
+      <c r="G103" s="51" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="104" spans="1:8" ht="33.75" hidden="1" x14ac:dyDescent="0.6">
+      <c r="A104" s="47" t="s">
+        <v>190</v>
+      </c>
+      <c r="B104" s="194" t="s">
+        <v>188</v>
+      </c>
+      <c r="C104" s="194"/>
+      <c r="D104" s="194"/>
+      <c r="E104" s="194"/>
+      <c r="F104" s="48" t="s">
+        <v>64</v>
+      </c>
+      <c r="G104" s="46" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="207"/>
-      <c r="C3" s="205" t="s">
-        <v>76</v>
-      </c>
-      <c r="D3" s="206"/>
-      <c r="E3" s="189"/>
-      <c r="F3" s="84" t="s">
-        <v>53</v>
-      </c>
-      <c r="G3" s="75"/>
-      <c r="H3" s="2"/>
-    </row>
-    <row r="4" spans="1:8" ht="33.75" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A4" s="192"/>
-      <c r="B4" s="208"/>
-      <c r="C4" s="102" t="s">
-        <v>42</v>
-      </c>
-      <c r="D4" s="103"/>
-      <c r="E4" s="101"/>
-      <c r="F4" s="85" t="s">
-        <v>53</v>
-      </c>
-      <c r="G4" s="86"/>
-    </row>
-    <row r="5" spans="1:8" ht="50.25" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A5" s="192"/>
-      <c r="B5" s="208"/>
-      <c r="C5" s="102" t="s">
-        <v>215</v>
-      </c>
-      <c r="D5" s="103"/>
-      <c r="E5" s="101"/>
-      <c r="F5" s="85" t="s">
-        <v>75</v>
-      </c>
-      <c r="G5" s="86"/>
-      <c r="H5" s="2"/>
-    </row>
-    <row r="6" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A6" s="192"/>
-      <c r="B6" s="208"/>
-      <c r="C6" s="97" t="s">
+    </row>
+    <row r="105" spans="1:8" ht="33.75" hidden="1" x14ac:dyDescent="0.6">
+      <c r="A105" s="45" t="s">
+        <v>178</v>
+      </c>
+      <c r="B105" s="192" t="s">
+        <v>179</v>
+      </c>
+      <c r="C105" s="192"/>
+      <c r="D105" s="192"/>
+      <c r="E105" s="192"/>
+      <c r="F105" s="44" t="s">
+        <v>64</v>
+      </c>
+      <c r="G105" s="46" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="106" spans="1:8" ht="128.25" hidden="1" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="A106" s="45" t="s">
+        <v>14</v>
+      </c>
+      <c r="B106" s="192" t="s">
+        <v>191</v>
+      </c>
+      <c r="C106" s="192"/>
+      <c r="D106" s="192"/>
+      <c r="E106" s="192"/>
+      <c r="F106" s="44" t="s">
         <v>65</v>
       </c>
-      <c r="D6" s="97"/>
-      <c r="E6" s="95"/>
-      <c r="F6" s="181" t="s">
-        <v>54</v>
-      </c>
-      <c r="G6" s="134"/>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.6">
-      <c r="A7" s="192"/>
-      <c r="B7" s="208"/>
-      <c r="C7" s="42" t="s">
+      <c r="G106" s="46" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="107" spans="1:8" ht="44.25" hidden="1" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="A107" s="45" t="s">
+        <v>180</v>
+      </c>
+      <c r="B107" s="192" t="s">
+        <v>181</v>
+      </c>
+      <c r="C107" s="192"/>
+      <c r="D107" s="192"/>
+      <c r="E107" s="192"/>
+      <c r="F107" s="44" t="s">
         <v>64</v>
       </c>
-      <c r="D7" s="89"/>
-      <c r="E7" s="90"/>
-      <c r="F7" s="182"/>
-      <c r="G7" s="190"/>
-    </row>
-    <row r="8" spans="1:8" ht="34.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.65">
-      <c r="A8" s="193"/>
-      <c r="B8" s="209"/>
-      <c r="C8" s="194" t="s">
-        <v>214</v>
-      </c>
-      <c r="D8" s="195"/>
-      <c r="E8" s="196"/>
-      <c r="F8" s="41" t="s">
-        <v>77</v>
-      </c>
-      <c r="G8" s="43"/>
-      <c r="H8" s="2"/>
-    </row>
-    <row r="10" spans="1:8" ht="19.899999999999999" thickBot="1" x14ac:dyDescent="0.65">
-      <c r="A10" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" ht="17.25" thickBot="1" x14ac:dyDescent="0.65">
-      <c r="A11" s="130" t="s">
-        <v>1</v>
-      </c>
-      <c r="B11" s="131"/>
-      <c r="C11" s="104" t="s">
-        <v>2</v>
-      </c>
-      <c r="D11" s="105"/>
-      <c r="E11" s="105"/>
-      <c r="F11" s="5" t="s">
-        <v>50</v>
-      </c>
-      <c r="G11" s="6" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" ht="37.5" customHeight="1" thickTop="1" x14ac:dyDescent="0.6">
-      <c r="A12" s="160" t="s">
-        <v>90</v>
-      </c>
-      <c r="B12" s="110" t="s">
-        <v>7</v>
-      </c>
-      <c r="C12" s="184" t="s">
-        <v>49</v>
-      </c>
-      <c r="D12" s="185"/>
-      <c r="E12" s="185"/>
-      <c r="F12" s="10">
-        <v>10</v>
-      </c>
-      <c r="G12" s="11"/>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.6">
-      <c r="A13" s="160"/>
-      <c r="B13" s="110"/>
-      <c r="C13" s="186" t="s">
-        <v>43</v>
-      </c>
-      <c r="D13" s="187"/>
-      <c r="E13" s="187"/>
-      <c r="F13" s="12">
-        <v>1</v>
-      </c>
-      <c r="G13" s="13"/>
-      <c r="H13" s="2"/>
-    </row>
-    <row r="14" spans="1:8" ht="37.5" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A14" s="160"/>
-      <c r="B14" s="110"/>
-      <c r="C14" s="186" t="s">
-        <v>78</v>
-      </c>
-      <c r="D14" s="187"/>
-      <c r="E14" s="187"/>
-      <c r="F14" s="12">
-        <v>1</v>
-      </c>
-      <c r="G14" s="13"/>
-    </row>
-    <row r="15" spans="1:8" ht="37.5" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A15" s="160"/>
-      <c r="B15" s="110"/>
-      <c r="C15" s="186" t="s">
-        <v>79</v>
-      </c>
-      <c r="D15" s="187"/>
-      <c r="E15" s="187"/>
-      <c r="F15" s="12">
-        <v>1</v>
-      </c>
-      <c r="G15" s="13"/>
-    </row>
-    <row r="16" spans="1:8" ht="37.5" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A16" s="160"/>
-      <c r="B16" s="110"/>
-      <c r="C16" s="186" t="s">
-        <v>80</v>
-      </c>
-      <c r="D16" s="187"/>
-      <c r="E16" s="187"/>
-      <c r="F16" s="12">
-        <v>1</v>
-      </c>
-      <c r="G16" s="13"/>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.6">
-      <c r="A17" s="160"/>
-      <c r="B17" s="110"/>
-      <c r="C17" s="186" t="s">
-        <v>81</v>
-      </c>
-      <c r="D17" s="187"/>
-      <c r="E17" s="187"/>
-      <c r="F17" s="12">
-        <v>1</v>
-      </c>
-      <c r="G17" s="13"/>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.6">
-      <c r="A18" s="160"/>
-      <c r="B18" s="110"/>
-      <c r="C18" s="186" t="s">
-        <v>82</v>
-      </c>
-      <c r="D18" s="187"/>
-      <c r="E18" s="187"/>
-      <c r="F18" s="12">
-        <v>1</v>
-      </c>
-      <c r="G18" s="13"/>
-      <c r="H18" s="2"/>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.6">
-      <c r="A19" s="160"/>
-      <c r="B19" s="110"/>
-      <c r="C19" s="186" t="s">
-        <v>83</v>
-      </c>
-      <c r="D19" s="187"/>
-      <c r="E19" s="187"/>
-      <c r="F19" s="12">
-        <v>1</v>
-      </c>
-      <c r="G19" s="13"/>
-    </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.6">
-      <c r="A20" s="160"/>
-      <c r="B20" s="110"/>
-      <c r="C20" s="186" t="s">
-        <v>84</v>
-      </c>
-      <c r="D20" s="187"/>
-      <c r="E20" s="187"/>
-      <c r="F20" s="12">
-        <v>1</v>
-      </c>
-      <c r="G20" s="13"/>
-    </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.6">
-      <c r="A21" s="160"/>
-      <c r="B21" s="110"/>
-      <c r="C21" s="186" t="s">
-        <v>85</v>
-      </c>
-      <c r="D21" s="187"/>
-      <c r="E21" s="187"/>
-      <c r="F21" s="12">
-        <v>1</v>
-      </c>
-      <c r="G21" s="13"/>
-      <c r="H21" s="2"/>
-    </row>
-    <row r="22" spans="1:8" ht="37.5" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A22" s="160"/>
-      <c r="B22" s="176"/>
-      <c r="C22" s="165" t="s">
-        <v>86</v>
-      </c>
-      <c r="D22" s="166"/>
-      <c r="E22" s="166"/>
-      <c r="F22" s="14">
-        <v>1</v>
-      </c>
-      <c r="G22" s="7"/>
-    </row>
-    <row r="23" spans="1:8" ht="50.65" x14ac:dyDescent="0.6">
-      <c r="A23" s="160"/>
-      <c r="B23" s="37" t="s">
-        <v>8</v>
-      </c>
-      <c r="C23" s="117" t="s">
-        <v>205</v>
-      </c>
-      <c r="D23" s="118"/>
-      <c r="E23" s="118"/>
-      <c r="F23" s="30" t="s">
-        <v>56</v>
-      </c>
-      <c r="G23" s="35"/>
-      <c r="H23" s="2"/>
-    </row>
-    <row r="24" spans="1:8" ht="33.75" x14ac:dyDescent="0.6">
-      <c r="A24" s="160"/>
-      <c r="B24" s="19" t="s">
-        <v>87</v>
-      </c>
-      <c r="C24" s="117" t="s">
-        <v>88</v>
-      </c>
-      <c r="D24" s="118"/>
-      <c r="E24" s="118"/>
-      <c r="F24" s="8" t="s">
-        <v>89</v>
-      </c>
-      <c r="G24" s="9"/>
-      <c r="H24" s="2"/>
-    </row>
-    <row r="25" spans="1:8" ht="33.75" x14ac:dyDescent="0.6">
-      <c r="A25" s="159" t="s">
-        <v>92</v>
-      </c>
-      <c r="B25" s="19" t="s">
-        <v>9</v>
-      </c>
-      <c r="C25" s="96" t="s">
-        <v>206</v>
-      </c>
-      <c r="D25" s="97"/>
-      <c r="E25" s="97"/>
-      <c r="F25" s="8" t="s">
-        <v>57</v>
-      </c>
-      <c r="G25" s="20"/>
-      <c r="H25" s="2"/>
-    </row>
-    <row r="26" spans="1:8" ht="51.75" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A26" s="160"/>
-      <c r="B26" s="19" t="s">
-        <v>7</v>
-      </c>
-      <c r="C26" s="117" t="s">
-        <v>91</v>
-      </c>
-      <c r="D26" s="118"/>
-      <c r="E26" s="118"/>
-      <c r="F26" s="8" t="s">
-        <v>58</v>
-      </c>
-      <c r="G26" s="71"/>
-      <c r="H26" s="2"/>
-    </row>
-    <row r="27" spans="1:8" ht="33.75" x14ac:dyDescent="0.6">
-      <c r="A27" s="160"/>
-      <c r="B27" s="19" t="s">
-        <v>10</v>
-      </c>
-      <c r="C27" s="96" t="s">
-        <v>200</v>
-      </c>
-      <c r="D27" s="97"/>
-      <c r="E27" s="97"/>
-      <c r="F27" s="8" t="s">
-        <v>59</v>
-      </c>
-      <c r="G27" s="20"/>
-    </row>
-    <row r="28" spans="1:8" ht="105.75" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A28" s="159" t="s">
-        <v>99</v>
-      </c>
-      <c r="B28" s="109" t="s">
-        <v>51</v>
-      </c>
-      <c r="C28" s="96" t="s">
-        <v>207</v>
-      </c>
-      <c r="D28" s="97"/>
-      <c r="E28" s="95"/>
-      <c r="F28" s="148" t="s">
-        <v>60</v>
-      </c>
-      <c r="G28" s="179"/>
-      <c r="H28" s="2"/>
-    </row>
-    <row r="29" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A29" s="160"/>
-      <c r="B29" s="176"/>
-      <c r="C29" s="62" t="s">
-        <v>198</v>
-      </c>
-      <c r="D29" s="63"/>
-      <c r="E29" s="64" t="s">
-        <v>213</v>
-      </c>
-      <c r="F29" s="149"/>
-      <c r="G29" s="180"/>
-    </row>
-    <row r="30" spans="1:8" ht="33.75" x14ac:dyDescent="0.6">
-      <c r="A30" s="160"/>
-      <c r="B30" s="19" t="s">
-        <v>11</v>
-      </c>
-      <c r="C30" s="96" t="s">
-        <v>93</v>
-      </c>
-      <c r="D30" s="97"/>
-      <c r="E30" s="97"/>
-      <c r="F30" s="8" t="s">
-        <v>61</v>
-      </c>
-      <c r="G30" s="20"/>
-      <c r="H30" s="2"/>
-    </row>
-    <row r="31" spans="1:8" ht="33.75" x14ac:dyDescent="0.6">
-      <c r="A31" s="160"/>
-      <c r="B31" s="34" t="s">
-        <v>12</v>
-      </c>
-      <c r="C31" s="167" t="s">
-        <v>94</v>
-      </c>
-      <c r="D31" s="168"/>
-      <c r="E31" s="168"/>
-      <c r="F31" s="39" t="s">
-        <v>95</v>
-      </c>
-      <c r="G31" s="35"/>
-    </row>
-    <row r="32" spans="1:8" ht="67.5" x14ac:dyDescent="0.6">
-      <c r="A32" s="183"/>
-      <c r="B32" s="21" t="s">
-        <v>96</v>
-      </c>
-      <c r="C32" s="167" t="s">
-        <v>97</v>
-      </c>
-      <c r="D32" s="168"/>
-      <c r="E32" s="168"/>
-      <c r="F32" s="22" t="s">
-        <v>98</v>
-      </c>
-      <c r="G32" s="9"/>
-      <c r="H32" s="2"/>
-    </row>
-    <row r="33" spans="1:8" ht="118.15" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A33" s="82" t="s">
-        <v>100</v>
-      </c>
-      <c r="B33" s="91"/>
-      <c r="C33" s="167" t="s">
-        <v>101</v>
-      </c>
-      <c r="D33" s="168"/>
-      <c r="E33" s="210"/>
-      <c r="F33" s="85" t="s">
-        <v>102</v>
-      </c>
-      <c r="G33" s="86"/>
-    </row>
-    <row r="34" spans="1:8" ht="50.65" x14ac:dyDescent="0.6">
-      <c r="A34" s="160" t="s">
-        <v>103</v>
-      </c>
-      <c r="B34" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="C34" s="186" t="s">
-        <v>55</v>
-      </c>
-      <c r="D34" s="187"/>
-      <c r="E34" s="187"/>
-      <c r="F34" s="16" t="s">
+      <c r="G107" s="46" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="108" spans="1:8" ht="115.5" hidden="1" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="A108" s="45" t="s">
+        <v>182</v>
+      </c>
+      <c r="B108" s="192" t="s">
+        <v>192</v>
+      </c>
+      <c r="C108" s="192"/>
+      <c r="D108" s="192"/>
+      <c r="E108" s="192"/>
+      <c r="F108" s="44" t="s">
         <v>104</v>
       </c>
-      <c r="G34" s="13"/>
-    </row>
-    <row r="35" spans="1:8" ht="33.75" x14ac:dyDescent="0.6">
-      <c r="A35" s="160"/>
-      <c r="B35" s="19" t="s">
-        <v>105</v>
-      </c>
-      <c r="C35" s="117" t="s">
-        <v>219</v>
-      </c>
-      <c r="D35" s="118"/>
-      <c r="E35" s="118"/>
-      <c r="F35" s="8" t="s">
-        <v>106</v>
-      </c>
-      <c r="G35" s="74"/>
-    </row>
-    <row r="36" spans="1:8" ht="33.75" x14ac:dyDescent="0.6">
-      <c r="A36" s="160"/>
-      <c r="B36" s="19" t="s">
-        <v>38</v>
-      </c>
-      <c r="C36" s="96" t="s">
-        <v>39</v>
-      </c>
-      <c r="D36" s="97"/>
-      <c r="E36" s="97"/>
-      <c r="F36" s="8" t="s">
-        <v>63</v>
-      </c>
-      <c r="G36" s="20"/>
-    </row>
-    <row r="37" spans="1:8" ht="50.65" x14ac:dyDescent="0.6">
-      <c r="A37" s="160"/>
-      <c r="B37" s="109" t="s">
-        <v>14</v>
-      </c>
-      <c r="C37" s="117" t="s">
-        <v>220</v>
-      </c>
-      <c r="D37" s="118"/>
-      <c r="E37" s="118"/>
-      <c r="F37" s="30" t="s">
-        <v>107</v>
-      </c>
-      <c r="G37" s="32"/>
-    </row>
-    <row r="38" spans="1:8" ht="57" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A38" s="160"/>
-      <c r="B38" s="110"/>
-      <c r="C38" s="143" t="s">
-        <v>221</v>
-      </c>
-      <c r="D38" s="144"/>
-      <c r="E38" s="144"/>
-      <c r="F38" s="30" t="s">
-        <v>68</v>
-      </c>
-      <c r="G38" s="71"/>
-      <c r="H38" s="2"/>
-    </row>
-    <row r="39" spans="1:8" ht="67.5" x14ac:dyDescent="0.6">
-      <c r="A39" s="162" t="s">
-        <v>109</v>
-      </c>
-      <c r="B39" s="21" t="s">
-        <v>15</v>
-      </c>
-      <c r="C39" s="118" t="s">
-        <v>110</v>
-      </c>
-      <c r="D39" s="118"/>
-      <c r="E39" s="118"/>
-      <c r="F39" s="8" t="s">
-        <v>111</v>
-      </c>
-      <c r="G39" s="9"/>
-    </row>
-    <row r="40" spans="1:8" ht="41.25" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A40" s="162"/>
-      <c r="B40" s="163" t="s">
-        <v>16</v>
-      </c>
-      <c r="C40" s="164" t="s">
-        <v>201</v>
-      </c>
-      <c r="D40" s="164"/>
-      <c r="E40" s="164"/>
-      <c r="F40" s="146" t="s">
-        <v>66</v>
-      </c>
-      <c r="G40" s="132"/>
-    </row>
-    <row r="41" spans="1:8" ht="32.25" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A41" s="162"/>
-      <c r="B41" s="163"/>
-      <c r="C41" s="92" t="s">
-        <v>112</v>
-      </c>
-      <c r="D41" s="197"/>
-      <c r="E41" s="198"/>
-      <c r="F41" s="147"/>
-      <c r="G41" s="132"/>
-    </row>
-    <row r="42" spans="1:8" ht="23.25" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A42" s="162"/>
-      <c r="B42" s="133" t="s">
-        <v>17</v>
-      </c>
-      <c r="C42" s="118" t="s">
-        <v>44</v>
-      </c>
-      <c r="D42" s="118"/>
-      <c r="E42" s="118"/>
-      <c r="F42" s="148" t="s">
-        <v>67</v>
-      </c>
-      <c r="G42" s="134"/>
-    </row>
-    <row r="43" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A43" s="162"/>
-      <c r="B43" s="133"/>
-      <c r="C43" s="65" t="s">
-        <v>113</v>
-      </c>
-      <c r="D43" s="150"/>
-      <c r="E43" s="151"/>
-      <c r="F43" s="149"/>
-      <c r="G43" s="134"/>
-    </row>
-    <row r="44" spans="1:8" ht="53.25" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A44" s="162"/>
-      <c r="B44" s="34" t="s">
-        <v>114</v>
-      </c>
-      <c r="C44" s="143" t="s">
-        <v>208</v>
-      </c>
-      <c r="D44" s="144"/>
-      <c r="E44" s="145"/>
-      <c r="F44" s="30" t="s">
-        <v>68</v>
-      </c>
-      <c r="G44" s="32"/>
-      <c r="H44" s="2"/>
-    </row>
-    <row r="45" spans="1:8" ht="158.25" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A45" s="137" t="s">
-        <v>115</v>
-      </c>
-      <c r="B45" s="36" t="s">
-        <v>116</v>
-      </c>
-      <c r="C45" s="140" t="s">
-        <v>202</v>
-      </c>
-      <c r="D45" s="141"/>
-      <c r="E45" s="142"/>
-      <c r="F45" s="38" t="s">
-        <v>117</v>
-      </c>
-      <c r="G45" s="32"/>
-    </row>
-    <row r="46" spans="1:8" ht="33.75" x14ac:dyDescent="0.6">
-      <c r="A46" s="138"/>
-      <c r="B46" s="36" t="s">
-        <v>118</v>
-      </c>
-      <c r="C46" s="140" t="s">
-        <v>125</v>
-      </c>
-      <c r="D46" s="141"/>
-      <c r="E46" s="142"/>
-      <c r="F46" s="38" t="s">
-        <v>126</v>
-      </c>
-      <c r="G46" s="32"/>
-    </row>
-    <row r="47" spans="1:8" ht="33.75" x14ac:dyDescent="0.6">
-      <c r="A47" s="138"/>
-      <c r="B47" s="36" t="s">
-        <v>119</v>
-      </c>
-      <c r="C47" s="140" t="s">
-        <v>222</v>
-      </c>
-      <c r="D47" s="141"/>
-      <c r="E47" s="142"/>
-      <c r="F47" s="38" t="s">
-        <v>127</v>
-      </c>
-      <c r="G47" s="32"/>
-    </row>
-    <row r="48" spans="1:8" ht="33.75" x14ac:dyDescent="0.6">
-      <c r="A48" s="138"/>
-      <c r="B48" s="36" t="s">
-        <v>120</v>
-      </c>
-      <c r="C48" s="140" t="s">
-        <v>128</v>
-      </c>
-      <c r="D48" s="141"/>
-      <c r="E48" s="142"/>
-      <c r="F48" s="38" t="s">
-        <v>129</v>
-      </c>
-      <c r="G48" s="32"/>
-    </row>
-    <row r="49" spans="1:8" ht="33.75" x14ac:dyDescent="0.6">
-      <c r="A49" s="138"/>
-      <c r="B49" s="36" t="s">
-        <v>121</v>
-      </c>
-      <c r="C49" s="140" t="s">
-        <v>130</v>
-      </c>
-      <c r="D49" s="141"/>
-      <c r="E49" s="142"/>
-      <c r="F49" s="38" t="s">
-        <v>131</v>
-      </c>
-      <c r="G49" s="32"/>
-    </row>
-    <row r="50" spans="1:8" ht="33.75" x14ac:dyDescent="0.6">
-      <c r="A50" s="139"/>
-      <c r="B50" s="36" t="s">
-        <v>122</v>
-      </c>
-      <c r="C50" s="140" t="s">
-        <v>132</v>
-      </c>
-      <c r="D50" s="141"/>
-      <c r="E50" s="142"/>
-      <c r="F50" s="38" t="s">
-        <v>133</v>
-      </c>
-      <c r="G50" s="32"/>
-    </row>
-    <row r="51" spans="1:8" ht="34.15" thickBot="1" x14ac:dyDescent="0.65">
-      <c r="A51" s="152" t="s">
-        <v>123</v>
-      </c>
-      <c r="B51" s="153"/>
-      <c r="C51" s="154" t="s">
-        <v>124</v>
-      </c>
-      <c r="D51" s="154"/>
-      <c r="E51" s="155"/>
-      <c r="F51" s="17" t="s">
-        <v>180</v>
-      </c>
-      <c r="G51" s="18"/>
-      <c r="H51" s="2"/>
-    </row>
-    <row r="53" spans="1:8" ht="19.899999999999999" thickBot="1" x14ac:dyDescent="0.65">
-      <c r="A53" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="54" spans="1:8" ht="17.25" thickBot="1" x14ac:dyDescent="0.65">
-      <c r="A54" s="130" t="s">
-        <v>1</v>
-      </c>
-      <c r="B54" s="131"/>
-      <c r="C54" s="104" t="s">
-        <v>2</v>
-      </c>
-      <c r="D54" s="105"/>
-      <c r="E54" s="105"/>
-      <c r="F54" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="G54" s="6" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="55" spans="1:8" ht="17.25" thickTop="1" x14ac:dyDescent="0.6">
-      <c r="A55" s="160" t="s">
-        <v>136</v>
-      </c>
-      <c r="B55" s="156" t="s">
-        <v>19</v>
-      </c>
-      <c r="C55" s="165" t="s">
-        <v>134</v>
-      </c>
-      <c r="D55" s="166"/>
-      <c r="E55" s="166"/>
-      <c r="F55" s="14" t="s">
-        <v>46</v>
-      </c>
-      <c r="G55" s="7"/>
-    </row>
-    <row r="56" spans="1:8" ht="53.25" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A56" s="160"/>
-      <c r="B56" s="110"/>
-      <c r="C56" s="167" t="s">
-        <v>199</v>
-      </c>
-      <c r="D56" s="168"/>
-      <c r="E56" s="168"/>
-      <c r="F56" s="21" t="s">
-        <v>46</v>
-      </c>
-      <c r="G56" s="76"/>
-    </row>
-    <row r="57" spans="1:8" x14ac:dyDescent="0.6">
-      <c r="A57" s="160"/>
-      <c r="B57" s="110"/>
-      <c r="C57" s="167" t="s">
-        <v>47</v>
-      </c>
-      <c r="D57" s="168"/>
-      <c r="E57" s="168"/>
-      <c r="F57" s="21" t="s">
-        <v>46</v>
-      </c>
-      <c r="G57" s="7"/>
-    </row>
-    <row r="58" spans="1:8" ht="33.75" x14ac:dyDescent="0.6">
-      <c r="A58" s="160"/>
-      <c r="B58" s="110"/>
-      <c r="C58" s="117" t="s">
+      <c r="G108" s="46" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="109" spans="1:8" ht="33.75" hidden="1" x14ac:dyDescent="0.6">
+      <c r="A109" s="45" t="s">
+        <v>183</v>
+      </c>
+      <c r="B109" s="192" t="s">
+        <v>184</v>
+      </c>
+      <c r="C109" s="192"/>
+      <c r="D109" s="192"/>
+      <c r="E109" s="192"/>
+      <c r="F109" s="44" t="s">
+        <v>64</v>
+      </c>
+      <c r="G109" s="46" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="110" spans="1:8" ht="34.15" hidden="1" thickBot="1" x14ac:dyDescent="0.65">
+      <c r="A110" s="53" t="s">
+        <v>185</v>
+      </c>
+      <c r="B110" s="195" t="s">
+        <v>186</v>
+      </c>
+      <c r="C110" s="195"/>
+      <c r="D110" s="195"/>
+      <c r="E110" s="195"/>
+      <c r="F110" s="54" t="s">
+        <v>64</v>
+      </c>
+      <c r="G110" s="55" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="111" spans="1:8" ht="26.25" hidden="1" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="A111" s="52" t="s">
+        <v>187</v>
+      </c>
+      <c r="B111" s="191" t="s">
+        <v>189</v>
+      </c>
+      <c r="C111" s="191"/>
+      <c r="D111" s="191"/>
+      <c r="E111" s="191"/>
+      <c r="F111" s="57" t="s">
+        <v>193</v>
+      </c>
+      <c r="G111" s="56">
+        <f>COUNTIF(G104:G110,"N")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="112" spans="1:8" hidden="1" x14ac:dyDescent="0.6"/>
+    <row r="113" spans="5:5" ht="17.25" thickTop="1" x14ac:dyDescent="0.6"/>
+    <row r="114" spans="5:5" x14ac:dyDescent="0.6">
+      <c r="E114" s="2" t="s">
         <v>209</v>
       </c>
-      <c r="D58" s="118"/>
-      <c r="E58" s="118"/>
-      <c r="F58" s="8" t="s">
-        <v>135</v>
-      </c>
-      <c r="G58" s="9"/>
-    </row>
-    <row r="59" spans="1:8" ht="102.75" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A59" s="160"/>
-      <c r="B59" s="110"/>
-      <c r="C59" s="117" t="s">
-        <v>137</v>
-      </c>
-      <c r="D59" s="118"/>
-      <c r="E59" s="158"/>
-      <c r="F59" s="30" t="s">
-        <v>52</v>
-      </c>
-      <c r="G59" s="32"/>
-    </row>
-    <row r="60" spans="1:8" ht="84" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A60" s="160"/>
-      <c r="B60" s="110"/>
-      <c r="C60" s="117" t="s">
-        <v>139</v>
-      </c>
-      <c r="D60" s="118"/>
-      <c r="E60" s="158"/>
-      <c r="F60" s="30" t="s">
-        <v>140</v>
-      </c>
-      <c r="G60" s="71"/>
-    </row>
-    <row r="61" spans="1:8" ht="118.15" x14ac:dyDescent="0.6">
-      <c r="A61" s="160"/>
-      <c r="B61" s="110"/>
-      <c r="C61" s="135" t="s">
-        <v>141</v>
-      </c>
-      <c r="D61" s="136"/>
-      <c r="E61" s="157"/>
-      <c r="F61" s="44" t="s">
-        <v>142</v>
-      </c>
-      <c r="G61" s="32"/>
-      <c r="H61" s="2"/>
-    </row>
-    <row r="62" spans="1:8" ht="33.75" x14ac:dyDescent="0.6">
-      <c r="A62" s="160"/>
-      <c r="B62" s="110"/>
-      <c r="C62" s="117" t="s">
-        <v>143</v>
-      </c>
-      <c r="D62" s="118"/>
-      <c r="E62" s="158"/>
-      <c r="F62" s="30" t="s">
-        <v>144</v>
-      </c>
-      <c r="G62" s="32"/>
-    </row>
-    <row r="63" spans="1:8" ht="102" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A63" s="160"/>
-      <c r="B63" s="19" t="s">
-        <v>145</v>
-      </c>
-      <c r="C63" s="169" t="s">
-        <v>146</v>
-      </c>
-      <c r="D63" s="170"/>
-      <c r="E63" s="170"/>
-      <c r="F63" s="68" t="s">
-        <v>148</v>
-      </c>
-      <c r="G63" s="9"/>
-    </row>
-    <row r="64" spans="1:8" ht="166.5" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A64" s="87" t="s">
-        <v>149</v>
-      </c>
-      <c r="B64" s="81"/>
-      <c r="C64" s="135" t="s">
-        <v>203</v>
-      </c>
-      <c r="D64" s="136"/>
-      <c r="E64" s="136"/>
-      <c r="F64" s="30" t="s">
-        <v>138</v>
-      </c>
-      <c r="G64" s="70"/>
-      <c r="H64" s="2"/>
-    </row>
-    <row r="65" spans="1:7" ht="101.25" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A65" s="87" t="s">
-        <v>150</v>
-      </c>
-      <c r="B65" s="81"/>
-      <c r="C65" s="135" t="s">
-        <v>154</v>
-      </c>
-      <c r="D65" s="136"/>
-      <c r="E65" s="136"/>
-      <c r="F65" s="30" t="s">
-        <v>155</v>
-      </c>
-      <c r="G65" s="35"/>
-    </row>
-    <row r="66" spans="1:7" ht="108" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A66" s="115" t="s">
-        <v>151</v>
-      </c>
-      <c r="B66" s="81"/>
-      <c r="C66" s="117" t="s">
-        <v>152</v>
-      </c>
-      <c r="D66" s="118"/>
-      <c r="E66" s="118"/>
-      <c r="F66" s="68" t="s">
-        <v>156</v>
-      </c>
-      <c r="G66" s="35"/>
-    </row>
-    <row r="67" spans="1:7" x14ac:dyDescent="0.6">
-      <c r="A67" s="175"/>
-      <c r="B67" s="81"/>
-      <c r="C67" s="102" t="s">
-        <v>153</v>
-      </c>
-      <c r="D67" s="103"/>
-      <c r="E67" s="101"/>
-      <c r="F67" s="68" t="s">
-        <v>147</v>
-      </c>
-      <c r="G67" s="32"/>
-    </row>
-    <row r="68" spans="1:7" ht="328.5" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A68" s="88" t="s">
-        <v>157</v>
-      </c>
-      <c r="B68" s="81"/>
-      <c r="C68" s="117" t="s">
-        <v>159</v>
-      </c>
-      <c r="D68" s="118"/>
-      <c r="E68" s="118"/>
-      <c r="F68" s="30" t="s">
-        <v>108</v>
-      </c>
-      <c r="G68" s="35"/>
-    </row>
-    <row r="69" spans="1:7" ht="51.75" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A69" s="159" t="s">
-        <v>158</v>
-      </c>
-      <c r="B69" s="37" t="s">
-        <v>20</v>
-      </c>
-      <c r="C69" s="199" t="s">
-        <v>223</v>
-      </c>
-      <c r="D69" s="200"/>
-      <c r="E69" s="201"/>
-      <c r="F69" s="8" t="s">
-        <v>69</v>
-      </c>
-      <c r="G69" s="20"/>
-    </row>
-    <row r="70" spans="1:7" ht="33.75" x14ac:dyDescent="0.6">
-      <c r="A70" s="160"/>
-      <c r="B70" s="109" t="s">
-        <v>34</v>
-      </c>
-      <c r="C70" s="177" t="s">
-        <v>224</v>
-      </c>
-      <c r="D70" s="178"/>
-      <c r="E70" s="178"/>
-      <c r="F70" s="66" t="s">
-        <v>161</v>
-      </c>
-      <c r="G70" s="69"/>
-    </row>
-    <row r="71" spans="1:7" x14ac:dyDescent="0.6">
-      <c r="A71" s="160"/>
-      <c r="B71" s="176"/>
-      <c r="C71" s="167" t="s">
-        <v>160</v>
-      </c>
-      <c r="D71" s="168"/>
-      <c r="E71" s="171"/>
-      <c r="F71" s="23" t="s">
-        <v>46</v>
-      </c>
-      <c r="G71" s="15"/>
-    </row>
-    <row r="72" spans="1:7" ht="33.75" x14ac:dyDescent="0.6">
-      <c r="A72" s="160"/>
-      <c r="B72" s="109" t="s">
-        <v>21</v>
-      </c>
-      <c r="C72" s="177" t="s">
-        <v>162</v>
-      </c>
-      <c r="D72" s="178"/>
-      <c r="E72" s="178"/>
-      <c r="F72" s="67" t="s">
-        <v>163</v>
-      </c>
-      <c r="G72" s="69"/>
-    </row>
-    <row r="73" spans="1:7" ht="33.75" x14ac:dyDescent="0.6">
-      <c r="A73" s="160"/>
-      <c r="B73" s="176"/>
-      <c r="C73" s="172" t="s">
-        <v>164</v>
-      </c>
-      <c r="D73" s="173"/>
-      <c r="E73" s="174"/>
-      <c r="F73" s="31" t="s">
-        <v>165</v>
-      </c>
-      <c r="G73" s="33"/>
-    </row>
-    <row r="74" spans="1:7" ht="33.75" x14ac:dyDescent="0.6">
-      <c r="A74" s="160"/>
-      <c r="B74" s="19" t="s">
-        <v>22</v>
-      </c>
-      <c r="C74" s="117" t="s">
-        <v>166</v>
-      </c>
-      <c r="D74" s="118"/>
-      <c r="E74" s="118"/>
-      <c r="F74" s="8" t="s">
-        <v>53</v>
-      </c>
-      <c r="G74" s="9"/>
-    </row>
-    <row r="75" spans="1:7" ht="33.75" x14ac:dyDescent="0.6">
-      <c r="A75" s="159" t="s">
-        <v>167</v>
-      </c>
-      <c r="B75" s="19" t="s">
-        <v>9</v>
-      </c>
-      <c r="C75" s="117" t="s">
-        <v>168</v>
-      </c>
-      <c r="D75" s="118"/>
-      <c r="E75" s="118"/>
-      <c r="F75" s="8" t="s">
-        <v>70</v>
-      </c>
-      <c r="G75" s="9"/>
-    </row>
-    <row r="76" spans="1:7" ht="33.75" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A76" s="160"/>
-      <c r="B76" s="37" t="s">
-        <v>23</v>
-      </c>
-      <c r="C76" s="96" t="s">
-        <v>169</v>
-      </c>
-      <c r="D76" s="97"/>
-      <c r="E76" s="97"/>
-      <c r="F76" s="30" t="s">
-        <v>62</v>
-      </c>
-      <c r="G76" s="35"/>
-    </row>
-    <row r="77" spans="1:7" ht="33.75" x14ac:dyDescent="0.6">
-      <c r="A77" s="160"/>
-      <c r="B77" s="109" t="s">
-        <v>24</v>
-      </c>
-      <c r="C77" s="117" t="s">
-        <v>170</v>
-      </c>
-      <c r="D77" s="118"/>
-      <c r="E77" s="118"/>
-      <c r="F77" s="8" t="s">
-        <v>71</v>
-      </c>
-      <c r="G77" s="9"/>
-    </row>
-    <row r="78" spans="1:7" ht="37.5" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A78" s="160"/>
-      <c r="B78" s="110"/>
-      <c r="C78" s="96" t="s">
-        <v>210</v>
-      </c>
-      <c r="D78" s="97"/>
-      <c r="E78" s="95"/>
-      <c r="F78" s="30" t="s">
-        <v>72</v>
-      </c>
-      <c r="G78" s="32"/>
-    </row>
-    <row r="79" spans="1:7" ht="33.75" x14ac:dyDescent="0.6">
-      <c r="A79" s="160"/>
-      <c r="B79" s="109" t="s">
-        <v>25</v>
-      </c>
-      <c r="C79" s="117" t="s">
-        <v>171</v>
-      </c>
-      <c r="D79" s="118"/>
-      <c r="E79" s="118"/>
-      <c r="F79" s="22" t="s">
-        <v>62</v>
-      </c>
-      <c r="G79" s="9"/>
-    </row>
-    <row r="80" spans="1:7" ht="33.75" x14ac:dyDescent="0.6">
-      <c r="A80" s="161"/>
-      <c r="B80" s="110"/>
-      <c r="C80" s="117" t="s">
-        <v>204</v>
-      </c>
-      <c r="D80" s="118"/>
-      <c r="E80" s="118"/>
-      <c r="F80" s="8" t="s">
-        <v>73</v>
-      </c>
-      <c r="G80" s="9"/>
-    </row>
-    <row r="81" spans="1:8" ht="33.75" x14ac:dyDescent="0.6">
-      <c r="A81" s="108" t="s">
-        <v>172</v>
-      </c>
-      <c r="B81" s="109" t="s">
-        <v>40</v>
-      </c>
-      <c r="C81" s="111" t="s">
-        <v>173</v>
-      </c>
-      <c r="D81" s="112"/>
-      <c r="E81" s="112"/>
-      <c r="F81" s="72" t="s">
-        <v>212</v>
-      </c>
-      <c r="G81" s="73"/>
-    </row>
-    <row r="82" spans="1:8" ht="33.75" x14ac:dyDescent="0.6">
-      <c r="A82" s="108"/>
-      <c r="B82" s="110"/>
-      <c r="C82" s="113" t="s">
-        <v>74</v>
-      </c>
-      <c r="D82" s="114"/>
-      <c r="E82" s="114"/>
-      <c r="F82" s="72" t="s">
-        <v>212</v>
-      </c>
-      <c r="G82" s="73"/>
-    </row>
-    <row r="83" spans="1:8" ht="33.75" x14ac:dyDescent="0.6">
-      <c r="A83" s="115" t="s">
-        <v>26</v>
-      </c>
-      <c r="B83" s="116"/>
-      <c r="C83" s="117" t="s">
-        <v>211</v>
-      </c>
-      <c r="D83" s="118"/>
-      <c r="E83" s="118"/>
-      <c r="F83" s="8" t="s">
-        <v>62</v>
-      </c>
-      <c r="G83" s="24"/>
-    </row>
-    <row r="84" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A84" s="124" t="s">
-        <v>35</v>
-      </c>
-      <c r="B84" s="25" t="s">
-        <v>27</v>
-      </c>
-      <c r="C84" s="126" t="s">
-        <v>217</v>
-      </c>
-      <c r="D84" s="127"/>
-      <c r="E84" s="127"/>
-      <c r="F84" s="25">
-        <v>3</v>
-      </c>
-      <c r="G84" s="26"/>
-    </row>
-    <row r="85" spans="1:8" ht="22.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.65">
-      <c r="A85" s="125"/>
-      <c r="B85" s="27" t="s">
-        <v>28</v>
-      </c>
-      <c r="C85" s="128" t="s">
-        <v>216</v>
-      </c>
-      <c r="D85" s="129"/>
-      <c r="E85" s="28"/>
-      <c r="F85" s="27">
-        <v>2</v>
-      </c>
-      <c r="G85" s="29"/>
-    </row>
-    <row r="86" spans="1:8" ht="17.25" thickTop="1" x14ac:dyDescent="0.6"/>
-    <row r="87" spans="1:8" ht="19.899999999999999" thickBot="1" x14ac:dyDescent="0.65">
-      <c r="A87" s="1" t="s">
-        <v>174</v>
-      </c>
-      <c r="B87" s="1"/>
-    </row>
-    <row r="88" spans="1:8" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.65">
-      <c r="A88" s="130" t="s">
-        <v>1</v>
-      </c>
-      <c r="B88" s="131"/>
-      <c r="C88" s="104" t="s">
-        <v>2</v>
-      </c>
-      <c r="D88" s="105"/>
-      <c r="E88" s="105"/>
-      <c r="F88" s="40" t="s">
-        <v>29</v>
-      </c>
-      <c r="G88" s="6" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="89" spans="1:8" ht="24" customHeight="1" thickTop="1" x14ac:dyDescent="0.6">
-      <c r="A89" s="217" t="s">
-        <v>31</v>
-      </c>
-      <c r="B89" s="202"/>
-      <c r="C89" s="106" t="s">
-        <v>36</v>
-      </c>
-      <c r="D89" s="107"/>
-      <c r="E89" s="107"/>
-      <c r="F89" s="14">
-        <v>5</v>
-      </c>
-      <c r="G89" s="7"/>
-    </row>
-    <row r="90" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A90" s="88" t="s">
-        <v>175</v>
-      </c>
-      <c r="B90" s="203"/>
-      <c r="C90" s="102" t="s">
-        <v>176</v>
-      </c>
-      <c r="D90" s="103"/>
-      <c r="E90" s="103"/>
-      <c r="F90" s="21">
-        <v>5</v>
-      </c>
-      <c r="G90" s="7"/>
-    </row>
-    <row r="91" spans="1:8" ht="43.5" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A91" s="88" t="s">
-        <v>48</v>
-      </c>
-      <c r="B91" s="203"/>
-      <c r="C91" s="102" t="s">
-        <v>177</v>
-      </c>
-      <c r="D91" s="103"/>
-      <c r="E91" s="103"/>
-      <c r="F91" s="21">
-        <v>5</v>
-      </c>
-      <c r="G91" s="7"/>
-    </row>
-    <row r="92" spans="1:8" ht="33.75" x14ac:dyDescent="0.6">
-      <c r="A92" s="88" t="s">
-        <v>32</v>
-      </c>
-      <c r="B92" s="203"/>
-      <c r="C92" s="102" t="s">
-        <v>37</v>
-      </c>
-      <c r="D92" s="103"/>
-      <c r="E92" s="103"/>
-      <c r="F92" s="34">
-        <v>5</v>
-      </c>
-      <c r="G92" s="32"/>
-    </row>
-    <row r="93" spans="1:8" ht="41.25" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A93" s="88" t="s">
-        <v>33</v>
-      </c>
-      <c r="B93" s="203"/>
-      <c r="C93" s="96" t="s">
-        <v>178</v>
-      </c>
-      <c r="D93" s="97"/>
-      <c r="E93" s="97"/>
-      <c r="F93" s="37">
-        <v>5</v>
-      </c>
-      <c r="G93" s="45"/>
-    </row>
-    <row r="94" spans="1:8" ht="74.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.65">
-      <c r="A94" s="218" t="s">
-        <v>179</v>
-      </c>
-      <c r="B94" s="216"/>
-      <c r="C94" s="99" t="s">
-        <v>218</v>
-      </c>
-      <c r="D94" s="100"/>
-      <c r="E94" s="98"/>
-      <c r="F94" s="46">
-        <v>10</v>
-      </c>
-      <c r="G94" s="47"/>
-      <c r="H94" s="2"/>
-    </row>
-    <row r="95" spans="1:8" ht="17.25" thickTop="1" x14ac:dyDescent="0.6">
-      <c r="A95" s="2"/>
-      <c r="B95" s="2"/>
-      <c r="C95" s="2"/>
-      <c r="D95" s="2"/>
-      <c r="E95" s="2"/>
-      <c r="F95" s="2"/>
-      <c r="G95" s="2"/>
-    </row>
-    <row r="96" spans="1:8" ht="19.899999999999999" thickBot="1" x14ac:dyDescent="0.65">
-      <c r="A96" s="1" t="s">
-        <v>225</v>
-      </c>
-      <c r="B96" s="1"/>
-    </row>
-    <row r="97" spans="1:8" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.65">
-      <c r="A97" s="130" t="s">
-        <v>1</v>
-      </c>
-      <c r="B97" s="131"/>
-      <c r="C97" s="104" t="s">
-        <v>2</v>
-      </c>
-      <c r="D97" s="105"/>
-      <c r="E97" s="105"/>
-      <c r="F97" s="79" t="s">
-        <v>29</v>
-      </c>
-      <c r="G97" s="6" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="98" spans="1:8" ht="39" customHeight="1" thickTop="1" x14ac:dyDescent="0.6">
-      <c r="A98" s="212" t="s">
-        <v>226</v>
-      </c>
-      <c r="B98" s="213"/>
-      <c r="C98" s="106" t="s">
-        <v>232</v>
-      </c>
-      <c r="D98" s="107"/>
-      <c r="E98" s="107"/>
-      <c r="F98" s="77" t="s">
-        <v>68</v>
-      </c>
-      <c r="G98" s="78"/>
-    </row>
-    <row r="99" spans="1:8" ht="39" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A99" s="214" t="s">
-        <v>227</v>
-      </c>
-      <c r="B99" s="203"/>
-      <c r="C99" s="102" t="s">
-        <v>233</v>
-      </c>
-      <c r="D99" s="103"/>
-      <c r="E99" s="103"/>
-      <c r="F99" s="77" t="s">
-        <v>68</v>
-      </c>
-      <c r="G99" s="78"/>
-    </row>
-    <row r="100" spans="1:8" ht="129.75" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A100" s="214" t="s">
-        <v>228</v>
-      </c>
-      <c r="B100" s="203"/>
-      <c r="C100" s="102" t="s">
-        <v>234</v>
-      </c>
-      <c r="D100" s="103"/>
-      <c r="E100" s="103"/>
-      <c r="F100" s="77" t="s">
-        <v>68</v>
-      </c>
-      <c r="G100" s="78"/>
-    </row>
-    <row r="101" spans="1:8" ht="49.5" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A101" s="214" t="s">
-        <v>229</v>
-      </c>
-      <c r="B101" s="203"/>
-      <c r="C101" s="102" t="s">
-        <v>235</v>
-      </c>
-      <c r="D101" s="103"/>
-      <c r="E101" s="101"/>
-      <c r="F101" s="77" t="s">
-        <v>68</v>
-      </c>
-      <c r="G101" s="80"/>
-    </row>
-    <row r="102" spans="1:8" ht="122.25" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A102" s="214" t="s">
-        <v>230</v>
-      </c>
-      <c r="B102" s="203"/>
-      <c r="C102" s="102" t="s">
-        <v>196</v>
-      </c>
-      <c r="D102" s="103"/>
-      <c r="E102" s="101"/>
-      <c r="F102" s="77" t="s">
-        <v>68</v>
-      </c>
-      <c r="G102" s="33"/>
-    </row>
-    <row r="103" spans="1:8" ht="38.25" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A103" s="211" t="s">
-        <v>231</v>
-      </c>
-      <c r="B103" s="204"/>
-      <c r="C103" s="96" t="s">
-        <v>236</v>
-      </c>
-      <c r="D103" s="97"/>
-      <c r="E103" s="97"/>
-      <c r="F103" s="77" t="s">
-        <v>68</v>
-      </c>
-      <c r="G103" s="45"/>
-    </row>
-    <row r="104" spans="1:8" ht="36.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.65">
-      <c r="A104" s="215" t="s">
-        <v>145</v>
-      </c>
-      <c r="B104" s="216"/>
-      <c r="C104" s="99" t="s">
-        <v>237</v>
-      </c>
-      <c r="D104" s="100"/>
-      <c r="E104" s="98"/>
-      <c r="F104" s="94" t="s">
-        <v>68</v>
-      </c>
-      <c r="G104" s="93"/>
-      <c r="H104" s="2"/>
-    </row>
-    <row r="105" spans="1:8" hidden="1" x14ac:dyDescent="0.6">
-      <c r="E105" s="3"/>
-    </row>
-    <row r="106" spans="1:8" hidden="1" x14ac:dyDescent="0.6"/>
-    <row r="107" spans="1:8" ht="19.5" hidden="1" x14ac:dyDescent="0.6">
-      <c r="A107" s="1" t="s">
-        <v>181</v>
-      </c>
-      <c r="B107" s="1"/>
-      <c r="C107" s="1"/>
-      <c r="D107" s="1"/>
-      <c r="E107" s="1"/>
-      <c r="F107" s="1"/>
-      <c r="G107" s="1"/>
-    </row>
-    <row r="108" spans="1:8" ht="26.25" hidden="1" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A108" s="53" t="s">
-        <v>1</v>
-      </c>
-      <c r="B108" s="121" t="s">
-        <v>2</v>
-      </c>
-      <c r="C108" s="121"/>
-      <c r="D108" s="121"/>
-      <c r="E108" s="121"/>
-      <c r="F108" s="54" t="s">
-        <v>41</v>
-      </c>
-      <c r="G108" s="55" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="109" spans="1:8" ht="33.75" hidden="1" x14ac:dyDescent="0.6">
-      <c r="A109" s="51" t="s">
-        <v>194</v>
-      </c>
-      <c r="B109" s="122" t="s">
-        <v>192</v>
-      </c>
-      <c r="C109" s="122"/>
-      <c r="D109" s="122"/>
-      <c r="E109" s="122"/>
-      <c r="F109" s="52" t="s">
-        <v>68</v>
-      </c>
-      <c r="G109" s="50" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="110" spans="1:8" ht="33.75" hidden="1" x14ac:dyDescent="0.6">
-      <c r="A110" s="49" t="s">
-        <v>182</v>
-      </c>
-      <c r="B110" s="120" t="s">
-        <v>183</v>
-      </c>
-      <c r="C110" s="120"/>
-      <c r="D110" s="120"/>
-      <c r="E110" s="120"/>
-      <c r="F110" s="48" t="s">
-        <v>68</v>
-      </c>
-      <c r="G110" s="50" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="111" spans="1:8" ht="128.25" hidden="1" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A111" s="49" t="s">
-        <v>15</v>
-      </c>
-      <c r="B111" s="120" t="s">
-        <v>195</v>
-      </c>
-      <c r="C111" s="120"/>
-      <c r="D111" s="120"/>
-      <c r="E111" s="120"/>
-      <c r="F111" s="48" t="s">
-        <v>69</v>
-      </c>
-      <c r="G111" s="50" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="112" spans="1:8" ht="44.25" hidden="1" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A112" s="49" t="s">
-        <v>184</v>
-      </c>
-      <c r="B112" s="120" t="s">
-        <v>185</v>
-      </c>
-      <c r="C112" s="120"/>
-      <c r="D112" s="120"/>
-      <c r="E112" s="120"/>
-      <c r="F112" s="48" t="s">
-        <v>68</v>
-      </c>
-      <c r="G112" s="50" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="113" spans="1:7" ht="115.5" hidden="1" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A113" s="49" t="s">
-        <v>186</v>
-      </c>
-      <c r="B113" s="120" t="s">
-        <v>196</v>
-      </c>
-      <c r="C113" s="120"/>
-      <c r="D113" s="120"/>
-      <c r="E113" s="120"/>
-      <c r="F113" s="48" t="s">
-        <v>108</v>
-      </c>
-      <c r="G113" s="50" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="114" spans="1:7" ht="33.75" hidden="1" x14ac:dyDescent="0.6">
-      <c r="A114" s="49" t="s">
-        <v>187</v>
-      </c>
-      <c r="B114" s="120" t="s">
-        <v>188</v>
-      </c>
-      <c r="C114" s="120"/>
-      <c r="D114" s="120"/>
-      <c r="E114" s="120"/>
-      <c r="F114" s="48" t="s">
-        <v>68</v>
-      </c>
-      <c r="G114" s="50" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="115" spans="1:7" ht="34.15" hidden="1" thickBot="1" x14ac:dyDescent="0.65">
-      <c r="A115" s="57" t="s">
-        <v>189</v>
-      </c>
-      <c r="B115" s="123" t="s">
-        <v>190</v>
-      </c>
-      <c r="C115" s="123"/>
-      <c r="D115" s="123"/>
-      <c r="E115" s="123"/>
-      <c r="F115" s="58" t="s">
-        <v>68</v>
-      </c>
-      <c r="G115" s="59" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="116" spans="1:7" ht="26.25" hidden="1" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A116" s="56" t="s">
-        <v>191</v>
-      </c>
-      <c r="B116" s="119" t="s">
-        <v>193</v>
-      </c>
-      <c r="C116" s="119"/>
-      <c r="D116" s="119"/>
-      <c r="E116" s="119"/>
-      <c r="F116" s="61" t="s">
-        <v>197</v>
-      </c>
-      <c r="G116" s="60">
-        <f>COUNTIF(G109:G115,"N")</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="117" spans="1:7" hidden="1" x14ac:dyDescent="0.6"/>
-    <row r="118" spans="1:7" ht="17.25" thickTop="1" x14ac:dyDescent="0.6"/>
-    <row r="119" spans="1:7" x14ac:dyDescent="0.6">
-      <c r="E119" s="2" t="s">
-        <v>213</v>
-      </c>
     </row>
   </sheetData>
-  <mergeCells count="141">
-    <mergeCell ref="C8:E8"/>
-    <mergeCell ref="B3:B8"/>
-    <mergeCell ref="A66:A67"/>
-    <mergeCell ref="D41:E41"/>
-    <mergeCell ref="C89:E89"/>
-    <mergeCell ref="C90:E90"/>
-    <mergeCell ref="C91:E91"/>
-    <mergeCell ref="C92:E92"/>
+  <mergeCells count="132">
+    <mergeCell ref="A78:A79"/>
+    <mergeCell ref="B78:B79"/>
+    <mergeCell ref="C78:E78"/>
+    <mergeCell ref="C79:E79"/>
+    <mergeCell ref="A80:B80"/>
+    <mergeCell ref="C80:E80"/>
+    <mergeCell ref="A81:A82"/>
+    <mergeCell ref="C81:E81"/>
+    <mergeCell ref="C82:D82"/>
+    <mergeCell ref="C57:E57"/>
+    <mergeCell ref="B111:E111"/>
+    <mergeCell ref="B108:E108"/>
+    <mergeCell ref="B103:E103"/>
+    <mergeCell ref="B104:E104"/>
+    <mergeCell ref="B105:E105"/>
+    <mergeCell ref="B106:E106"/>
+    <mergeCell ref="B107:E107"/>
+    <mergeCell ref="B109:E109"/>
+    <mergeCell ref="B110:E110"/>
     <mergeCell ref="C93:E93"/>
     <mergeCell ref="C94:E94"/>
-    <mergeCell ref="C65:E65"/>
-    <mergeCell ref="A69:A74"/>
-    <mergeCell ref="C69:E69"/>
-    <mergeCell ref="B70:B71"/>
+    <mergeCell ref="C95:E95"/>
+    <mergeCell ref="C98:E98"/>
+    <mergeCell ref="C99:E99"/>
+    <mergeCell ref="C96:E96"/>
+    <mergeCell ref="C97:E97"/>
     <mergeCell ref="C70:E70"/>
-    <mergeCell ref="C78:E78"/>
+    <mergeCell ref="C71:E71"/>
+    <mergeCell ref="G38:G39"/>
+    <mergeCell ref="B40:B41"/>
+    <mergeCell ref="C40:E40"/>
+    <mergeCell ref="G40:G41"/>
+    <mergeCell ref="C61:E61"/>
+    <mergeCell ref="A43:A48"/>
+    <mergeCell ref="C45:E45"/>
+    <mergeCell ref="C46:E46"/>
+    <mergeCell ref="C42:E42"/>
+    <mergeCell ref="C44:E44"/>
+    <mergeCell ref="F38:F39"/>
+    <mergeCell ref="F40:F41"/>
+    <mergeCell ref="D41:E41"/>
+    <mergeCell ref="A49:B49"/>
+    <mergeCell ref="C49:E49"/>
+    <mergeCell ref="C47:E47"/>
+    <mergeCell ref="C48:E48"/>
+    <mergeCell ref="B52:B59"/>
+    <mergeCell ref="C58:E58"/>
+    <mergeCell ref="C56:E56"/>
+    <mergeCell ref="G26:G27"/>
+    <mergeCell ref="F5:F6"/>
     <mergeCell ref="C20:E20"/>
+    <mergeCell ref="C22:E22"/>
+    <mergeCell ref="A23:A25"/>
+    <mergeCell ref="C23:E23"/>
+    <mergeCell ref="C24:E24"/>
+    <mergeCell ref="C25:E25"/>
+    <mergeCell ref="A26:A30"/>
+    <mergeCell ref="B26:B27"/>
+    <mergeCell ref="C26:E26"/>
+    <mergeCell ref="C28:E28"/>
+    <mergeCell ref="C30:E30"/>
+    <mergeCell ref="A10:A22"/>
+    <mergeCell ref="B10:B20"/>
+    <mergeCell ref="C10:E10"/>
+    <mergeCell ref="G5:G6"/>
+    <mergeCell ref="A2:A7"/>
+    <mergeCell ref="C2:E2"/>
+    <mergeCell ref="C3:E3"/>
+    <mergeCell ref="C4:E4"/>
+    <mergeCell ref="C5:E5"/>
+    <mergeCell ref="F26:F27"/>
     <mergeCell ref="C21:E21"/>
-    <mergeCell ref="C36:E36"/>
-    <mergeCell ref="B37:B38"/>
-    <mergeCell ref="C37:E37"/>
-    <mergeCell ref="C38:E38"/>
-    <mergeCell ref="F28:F29"/>
-    <mergeCell ref="C23:E23"/>
+    <mergeCell ref="C29:E29"/>
     <mergeCell ref="C31:E31"/>
+    <mergeCell ref="A32:A36"/>
+    <mergeCell ref="C32:E32"/>
     <mergeCell ref="C33:E33"/>
-    <mergeCell ref="A34:A38"/>
-    <mergeCell ref="C34:E34"/>
-    <mergeCell ref="C35:E35"/>
+    <mergeCell ref="C11:E11"/>
+    <mergeCell ref="C12:E12"/>
     <mergeCell ref="C13:E13"/>
     <mergeCell ref="C14:E14"/>
     <mergeCell ref="C15:E15"/>
     <mergeCell ref="C16:E16"/>
     <mergeCell ref="C17:E17"/>
+    <mergeCell ref="C90:E90"/>
+    <mergeCell ref="C62:E62"/>
+    <mergeCell ref="A66:A71"/>
+    <mergeCell ref="C66:E66"/>
+    <mergeCell ref="B67:B68"/>
+    <mergeCell ref="C67:E67"/>
+    <mergeCell ref="C75:E75"/>
     <mergeCell ref="C18:E18"/>
     <mergeCell ref="C19:E19"/>
-    <mergeCell ref="B2:E2"/>
-    <mergeCell ref="G6:G7"/>
-    <mergeCell ref="A11:B11"/>
-    <mergeCell ref="C11:E11"/>
-    <mergeCell ref="A3:A8"/>
-    <mergeCell ref="C3:E3"/>
-    <mergeCell ref="C4:E4"/>
-    <mergeCell ref="C5:E5"/>
-    <mergeCell ref="C6:E6"/>
-    <mergeCell ref="C66:E66"/>
-    <mergeCell ref="C67:E67"/>
-    <mergeCell ref="C68:E68"/>
-    <mergeCell ref="B72:B73"/>
+    <mergeCell ref="C34:E34"/>
+    <mergeCell ref="B35:B36"/>
+    <mergeCell ref="C35:E35"/>
+    <mergeCell ref="C36:E36"/>
+    <mergeCell ref="C63:E63"/>
+    <mergeCell ref="C64:E64"/>
+    <mergeCell ref="C65:E65"/>
+    <mergeCell ref="B69:B70"/>
+    <mergeCell ref="C69:E69"/>
+    <mergeCell ref="A72:A77"/>
     <mergeCell ref="C72:E72"/>
-    <mergeCell ref="G28:G29"/>
-    <mergeCell ref="F6:F7"/>
-    <mergeCell ref="C22:E22"/>
-    <mergeCell ref="C24:E24"/>
-    <mergeCell ref="A25:A27"/>
-    <mergeCell ref="C25:E25"/>
-    <mergeCell ref="C26:E26"/>
-    <mergeCell ref="C27:E27"/>
-    <mergeCell ref="A28:A32"/>
-    <mergeCell ref="B28:B29"/>
-    <mergeCell ref="C28:E28"/>
-    <mergeCell ref="C30:E30"/>
-    <mergeCell ref="C32:E32"/>
-    <mergeCell ref="A12:A24"/>
-    <mergeCell ref="B12:B22"/>
-    <mergeCell ref="C12:E12"/>
-    <mergeCell ref="A75:A80"/>
-    <mergeCell ref="C75:E75"/>
+    <mergeCell ref="C73:E73"/>
+    <mergeCell ref="B74:B75"/>
+    <mergeCell ref="C74:E74"/>
+    <mergeCell ref="B76:B77"/>
+    <mergeCell ref="C7:E7"/>
+    <mergeCell ref="B2:B7"/>
+    <mergeCell ref="A63:A64"/>
+    <mergeCell ref="D39:E39"/>
+    <mergeCell ref="C85:E85"/>
+    <mergeCell ref="C86:E86"/>
+    <mergeCell ref="C87:E87"/>
+    <mergeCell ref="C88:E88"/>
+    <mergeCell ref="C89:E89"/>
     <mergeCell ref="C76:E76"/>
-    <mergeCell ref="B77:B78"/>
-    <mergeCell ref="C77:E77"/>
-    <mergeCell ref="B79:B80"/>
-    <mergeCell ref="C79:E79"/>
-    <mergeCell ref="A39:A44"/>
-    <mergeCell ref="C39:E39"/>
-    <mergeCell ref="B40:B41"/>
-    <mergeCell ref="C40:E40"/>
-    <mergeCell ref="C45:E45"/>
-    <mergeCell ref="A55:A63"/>
+    <mergeCell ref="A37:A42"/>
+    <mergeCell ref="C37:E37"/>
+    <mergeCell ref="B38:B39"/>
+    <mergeCell ref="C38:E38"/>
+    <mergeCell ref="C43:E43"/>
+    <mergeCell ref="A52:A60"/>
+    <mergeCell ref="C52:E52"/>
+    <mergeCell ref="C53:E53"/>
+    <mergeCell ref="C54:E54"/>
     <mergeCell ref="C55:E55"/>
-    <mergeCell ref="C56:E56"/>
-    <mergeCell ref="C57:E57"/>
-    <mergeCell ref="C58:E58"/>
-    <mergeCell ref="C62:E62"/>
-    <mergeCell ref="C63:E63"/>
-    <mergeCell ref="C80:E80"/>
-    <mergeCell ref="C71:E71"/>
-    <mergeCell ref="C73:E73"/>
-    <mergeCell ref="C74:E74"/>
-    <mergeCell ref="G40:G41"/>
-    <mergeCell ref="B42:B43"/>
-    <mergeCell ref="C42:E42"/>
-    <mergeCell ref="G42:G43"/>
-    <mergeCell ref="C64:E64"/>
-    <mergeCell ref="A45:A50"/>
-    <mergeCell ref="C47:E47"/>
-    <mergeCell ref="C48:E48"/>
-    <mergeCell ref="C44:E44"/>
-    <mergeCell ref="C46:E46"/>
-    <mergeCell ref="F40:F41"/>
-    <mergeCell ref="F42:F43"/>
-    <mergeCell ref="D43:E43"/>
-    <mergeCell ref="A51:B51"/>
-    <mergeCell ref="C51:E51"/>
-    <mergeCell ref="A54:B54"/>
-    <mergeCell ref="C54:E54"/>
-    <mergeCell ref="C49:E49"/>
-    <mergeCell ref="C50:E50"/>
-    <mergeCell ref="B55:B62"/>
-    <mergeCell ref="C61:E61"/>
     <mergeCell ref="C59:E59"/>
     <mergeCell ref="C60:E60"/>
-    <mergeCell ref="B116:E116"/>
-    <mergeCell ref="B113:E113"/>
-    <mergeCell ref="B108:E108"/>
-    <mergeCell ref="B109:E109"/>
-    <mergeCell ref="B110:E110"/>
-    <mergeCell ref="B111:E111"/>
-    <mergeCell ref="B112:E112"/>
-    <mergeCell ref="B114:E114"/>
-    <mergeCell ref="B115:E115"/>
-    <mergeCell ref="C97:E97"/>
-    <mergeCell ref="C98:E98"/>
-    <mergeCell ref="C99:E99"/>
-    <mergeCell ref="C100:E100"/>
-    <mergeCell ref="A81:A82"/>
-    <mergeCell ref="B81:B82"/>
-    <mergeCell ref="C81:E81"/>
-    <mergeCell ref="C82:E82"/>
-    <mergeCell ref="A83:B83"/>
-    <mergeCell ref="C83:E83"/>
-    <mergeCell ref="A84:A85"/>
-    <mergeCell ref="C84:E84"/>
-    <mergeCell ref="C85:D85"/>
-    <mergeCell ref="A88:B88"/>
-    <mergeCell ref="C88:E88"/>
-    <mergeCell ref="A97:B97"/>
-    <mergeCell ref="C103:E103"/>
-    <mergeCell ref="C104:E104"/>
-    <mergeCell ref="C101:E101"/>
-    <mergeCell ref="C102:E102"/>
+    <mergeCell ref="C77:E77"/>
+    <mergeCell ref="C68:E68"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.70866141732283472" right="0.70866141732283472" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup paperSize="9" scale="64" fitToHeight="0" orientation="portrait" blackAndWhite="1" r:id="rId1"/>
   <rowBreaks count="3" manualBreakCount="3">
-    <brk id="51" max="6" man="1"/>
-    <brk id="85" max="6" man="1"/>
-    <brk id="104" max="16383" man="1"/>
+    <brk id="49" max="6" man="1"/>
+    <brk id="82" max="6" man="1"/>
+    <brk id="99" max="16383" man="1"/>
   </rowBreaks>
   <drawing r:id="rId2"/>
 </worksheet>

--- a/mafra.xlsx
+++ b/mafra.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\works\anti\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9CCCB4EB-AF34-47DA-8184-89E6FB8C437E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA92205A-732C-4FC7-B62D-B7E1D46C2F6E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15796" tabRatio="728" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1635,7 +1635,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="96">
+  <borders count="102">
     <border>
       <left/>
       <right/>
@@ -2838,6 +2838,92 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="double">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="double">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -3126,95 +3212,137 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="88" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="79" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="95" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="79" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="54" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="59" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="57" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="61" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="62" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="86" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="61" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="62" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="80" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="95" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="79" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="70" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="71" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="92" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="93" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="94" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="10" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="10" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="61" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="62" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="80" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="57" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="77" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="top" wrapText="1"/>
@@ -3222,35 +3350,137 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="74" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="75" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="76" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="66" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="64" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="67" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="68" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="69" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="90" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="91" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="center" wrapText="1"/>
@@ -3258,93 +3488,51 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="64" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="67" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="68" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="69" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="90" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="91" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="66" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="81" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="70" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="71" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="92" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="93" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="94" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="10" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="10" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -3353,18 +3541,6 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -3375,113 +3551,23 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="57" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="77" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="74" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="75" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="76" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="96" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="86" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="54" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="59" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="57" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="61" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="62" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="97" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="98" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="99" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="100" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="101" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="5">
@@ -3874,15 +3960,15 @@
       </c>
     </row>
     <row r="2" spans="1:8" ht="34.15" customHeight="1" thickTop="1" x14ac:dyDescent="0.6">
-      <c r="A2" s="145" t="s">
+      <c r="A2" s="172" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="103"/>
-      <c r="C2" s="148" t="s">
+      <c r="B2" s="190"/>
+      <c r="C2" s="175" t="s">
         <v>72</v>
       </c>
-      <c r="D2" s="149"/>
-      <c r="E2" s="150"/>
+      <c r="D2" s="176"/>
+      <c r="E2" s="177"/>
       <c r="F2" s="78" t="s">
         <v>49</v>
       </c>
@@ -3890,26 +3976,26 @@
       <c r="H2" s="2"/>
     </row>
     <row r="3" spans="1:8" ht="33.75" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A3" s="146"/>
-      <c r="B3" s="104"/>
-      <c r="C3" s="112" t="s">
+      <c r="A3" s="173"/>
+      <c r="B3" s="191"/>
+      <c r="C3" s="119" t="s">
         <v>40</v>
       </c>
-      <c r="D3" s="113"/>
-      <c r="E3" s="151"/>
+      <c r="D3" s="120"/>
+      <c r="E3" s="126"/>
       <c r="F3" s="79" t="s">
         <v>49</v>
       </c>
       <c r="G3" s="80"/>
     </row>
     <row r="4" spans="1:8" ht="50.25" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A4" s="146"/>
-      <c r="B4" s="104"/>
-      <c r="C4" s="112" t="s">
+      <c r="A4" s="173"/>
+      <c r="B4" s="191"/>
+      <c r="C4" s="119" t="s">
         <v>211</v>
       </c>
-      <c r="D4" s="113"/>
-      <c r="E4" s="151"/>
+      <c r="D4" s="120"/>
+      <c r="E4" s="126"/>
       <c r="F4" s="79" t="s">
         <v>71</v>
       </c>
@@ -3917,37 +4003,37 @@
       <c r="H4" s="2"/>
     </row>
     <row r="5" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A5" s="146"/>
-      <c r="B5" s="104"/>
-      <c r="C5" s="115" t="s">
+      <c r="A5" s="173"/>
+      <c r="B5" s="191"/>
+      <c r="C5" s="122" t="s">
         <v>61</v>
       </c>
-      <c r="D5" s="115"/>
-      <c r="E5" s="130"/>
-      <c r="F5" s="154" t="s">
+      <c r="D5" s="122"/>
+      <c r="E5" s="166"/>
+      <c r="F5" s="158" t="s">
         <v>50</v>
       </c>
-      <c r="G5" s="143"/>
+      <c r="G5" s="132"/>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.6">
-      <c r="A6" s="146"/>
-      <c r="B6" s="104"/>
+      <c r="A6" s="173"/>
+      <c r="B6" s="191"/>
       <c r="C6" s="38" t="s">
         <v>60</v>
       </c>
       <c r="D6" s="83"/>
       <c r="E6" s="84"/>
-      <c r="F6" s="155"/>
-      <c r="G6" s="144"/>
+      <c r="F6" s="159"/>
+      <c r="G6" s="171"/>
     </row>
     <row r="7" spans="1:8" ht="34.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.65">
-      <c r="A7" s="147"/>
-      <c r="B7" s="105"/>
-      <c r="C7" s="100" t="s">
+      <c r="A7" s="174"/>
+      <c r="B7" s="192"/>
+      <c r="C7" s="187" t="s">
         <v>210</v>
       </c>
-      <c r="D7" s="101"/>
-      <c r="E7" s="102"/>
+      <c r="D7" s="188"/>
+      <c r="E7" s="189"/>
       <c r="F7" s="37" t="s">
         <v>73</v>
       </c>
@@ -3960,30 +4046,30 @@
       </c>
     </row>
     <row r="10" spans="1:8" ht="37.5" customHeight="1" thickTop="1" x14ac:dyDescent="0.6">
-      <c r="A10" s="122" t="s">
+      <c r="A10" s="163" t="s">
         <v>86</v>
       </c>
-      <c r="B10" s="133" t="s">
+      <c r="B10" s="97" t="s">
         <v>6</v>
       </c>
-      <c r="C10" s="159" t="s">
+      <c r="C10" s="169" t="s">
         <v>46</v>
       </c>
-      <c r="D10" s="160"/>
-      <c r="E10" s="160"/>
+      <c r="D10" s="170"/>
+      <c r="E10" s="170"/>
       <c r="F10" s="7">
         <v>10</v>
       </c>
       <c r="G10" s="8"/>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.6">
-      <c r="A11" s="122"/>
-      <c r="B11" s="133"/>
-      <c r="C11" s="131" t="s">
+      <c r="A11" s="163"/>
+      <c r="B11" s="97"/>
+      <c r="C11" s="179" t="s">
         <v>41</v>
       </c>
-      <c r="D11" s="132"/>
-      <c r="E11" s="132"/>
+      <c r="D11" s="180"/>
+      <c r="E11" s="180"/>
       <c r="F11" s="9">
         <v>1</v>
       </c>
@@ -3991,65 +4077,65 @@
       <c r="H11" s="2"/>
     </row>
     <row r="12" spans="1:8" ht="37.5" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A12" s="122"/>
-      <c r="B12" s="133"/>
-      <c r="C12" s="131" t="s">
+      <c r="A12" s="163"/>
+      <c r="B12" s="97"/>
+      <c r="C12" s="179" t="s">
         <v>74</v>
       </c>
-      <c r="D12" s="132"/>
-      <c r="E12" s="132"/>
+      <c r="D12" s="180"/>
+      <c r="E12" s="180"/>
       <c r="F12" s="9">
         <v>1</v>
       </c>
       <c r="G12" s="10"/>
     </row>
     <row r="13" spans="1:8" ht="37.5" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A13" s="122"/>
-      <c r="B13" s="133"/>
-      <c r="C13" s="131" t="s">
+      <c r="A13" s="163"/>
+      <c r="B13" s="97"/>
+      <c r="C13" s="179" t="s">
         <v>75</v>
       </c>
-      <c r="D13" s="132"/>
-      <c r="E13" s="132"/>
+      <c r="D13" s="180"/>
+      <c r="E13" s="180"/>
       <c r="F13" s="9">
         <v>1</v>
       </c>
       <c r="G13" s="10"/>
     </row>
     <row r="14" spans="1:8" ht="37.5" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A14" s="122"/>
-      <c r="B14" s="133"/>
-      <c r="C14" s="131" t="s">
+      <c r="A14" s="163"/>
+      <c r="B14" s="97"/>
+      <c r="C14" s="179" t="s">
         <v>76</v>
       </c>
-      <c r="D14" s="132"/>
-      <c r="E14" s="132"/>
+      <c r="D14" s="180"/>
+      <c r="E14" s="180"/>
       <c r="F14" s="9">
         <v>1</v>
       </c>
       <c r="G14" s="10"/>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.6">
-      <c r="A15" s="122"/>
-      <c r="B15" s="133"/>
-      <c r="C15" s="131" t="s">
+      <c r="A15" s="163"/>
+      <c r="B15" s="97"/>
+      <c r="C15" s="179" t="s">
         <v>77</v>
       </c>
-      <c r="D15" s="132"/>
-      <c r="E15" s="132"/>
+      <c r="D15" s="180"/>
+      <c r="E15" s="180"/>
       <c r="F15" s="9">
         <v>1</v>
       </c>
       <c r="G15" s="10"/>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.6">
-      <c r="A16" s="122"/>
-      <c r="B16" s="133"/>
-      <c r="C16" s="131" t="s">
+      <c r="A16" s="163"/>
+      <c r="B16" s="97"/>
+      <c r="C16" s="179" t="s">
         <v>78</v>
       </c>
-      <c r="D16" s="132"/>
-      <c r="E16" s="132"/>
+      <c r="D16" s="180"/>
+      <c r="E16" s="180"/>
       <c r="F16" s="9">
         <v>1</v>
       </c>
@@ -4057,39 +4143,39 @@
       <c r="H16" s="2"/>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.6">
-      <c r="A17" s="122"/>
-      <c r="B17" s="133"/>
-      <c r="C17" s="131" t="s">
+      <c r="A17" s="163"/>
+      <c r="B17" s="97"/>
+      <c r="C17" s="179" t="s">
         <v>79</v>
       </c>
-      <c r="D17" s="132"/>
-      <c r="E17" s="132"/>
+      <c r="D17" s="180"/>
+      <c r="E17" s="180"/>
       <c r="F17" s="9">
         <v>1</v>
       </c>
       <c r="G17" s="10"/>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.6">
-      <c r="A18" s="122"/>
-      <c r="B18" s="133"/>
-      <c r="C18" s="131" t="s">
+      <c r="A18" s="163"/>
+      <c r="B18" s="97"/>
+      <c r="C18" s="179" t="s">
         <v>80</v>
       </c>
-      <c r="D18" s="132"/>
-      <c r="E18" s="132"/>
+      <c r="D18" s="180"/>
+      <c r="E18" s="180"/>
       <c r="F18" s="9">
         <v>1</v>
       </c>
       <c r="G18" s="10"/>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.6">
-      <c r="A19" s="122"/>
-      <c r="B19" s="133"/>
-      <c r="C19" s="131" t="s">
+      <c r="A19" s="163"/>
+      <c r="B19" s="97"/>
+      <c r="C19" s="179" t="s">
         <v>81</v>
       </c>
-      <c r="D19" s="132"/>
-      <c r="E19" s="132"/>
+      <c r="D19" s="180"/>
+      <c r="E19" s="180"/>
       <c r="F19" s="9">
         <v>1</v>
       </c>
@@ -4097,28 +4183,28 @@
       <c r="H19" s="2"/>
     </row>
     <row r="20" spans="1:8" ht="37.5" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A20" s="122"/>
-      <c r="B20" s="127"/>
-      <c r="C20" s="156" t="s">
+      <c r="A20" s="163"/>
+      <c r="B20" s="165"/>
+      <c r="C20" s="160" t="s">
         <v>82</v>
       </c>
-      <c r="D20" s="157"/>
-      <c r="E20" s="157"/>
+      <c r="D20" s="161"/>
+      <c r="E20" s="161"/>
       <c r="F20" s="11">
         <v>1</v>
       </c>
       <c r="G20" s="4"/>
     </row>
     <row r="21" spans="1:8" ht="50.65" x14ac:dyDescent="0.6">
-      <c r="A21" s="122"/>
+      <c r="A21" s="163"/>
       <c r="B21" s="34" t="s">
         <v>7</v>
       </c>
-      <c r="C21" s="134" t="s">
+      <c r="C21" s="103" t="s">
         <v>201</v>
       </c>
-      <c r="D21" s="135"/>
-      <c r="E21" s="135"/>
+      <c r="D21" s="104"/>
+      <c r="E21" s="104"/>
       <c r="F21" s="27" t="s">
         <v>52</v>
       </c>
@@ -4126,15 +4212,15 @@
       <c r="H21" s="2"/>
     </row>
     <row r="22" spans="1:8" ht="33.75" x14ac:dyDescent="0.6">
-      <c r="A22" s="122"/>
+      <c r="A22" s="163"/>
       <c r="B22" s="16" t="s">
         <v>83</v>
       </c>
-      <c r="C22" s="134" t="s">
+      <c r="C22" s="103" t="s">
         <v>84</v>
       </c>
-      <c r="D22" s="135"/>
-      <c r="E22" s="135"/>
+      <c r="D22" s="104"/>
+      <c r="E22" s="104"/>
       <c r="F22" s="5" t="s">
         <v>85</v>
       </c>
@@ -4142,17 +4228,17 @@
       <c r="H22" s="2"/>
     </row>
     <row r="23" spans="1:8" ht="33.75" x14ac:dyDescent="0.6">
-      <c r="A23" s="121" t="s">
+      <c r="A23" s="162" t="s">
         <v>88</v>
       </c>
       <c r="B23" s="16" t="s">
         <v>8</v>
       </c>
-      <c r="C23" s="114" t="s">
+      <c r="C23" s="121" t="s">
         <v>202</v>
       </c>
-      <c r="D23" s="115"/>
-      <c r="E23" s="115"/>
+      <c r="D23" s="122"/>
+      <c r="E23" s="122"/>
       <c r="F23" s="5" t="s">
         <v>53</v>
       </c>
@@ -4160,15 +4246,15 @@
       <c r="H23" s="2"/>
     </row>
     <row r="24" spans="1:8" ht="51.75" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A24" s="122"/>
+      <c r="A24" s="163"/>
       <c r="B24" s="16" t="s">
         <v>6</v>
       </c>
-      <c r="C24" s="134" t="s">
+      <c r="C24" s="103" t="s">
         <v>87</v>
       </c>
-      <c r="D24" s="135"/>
-      <c r="E24" s="135"/>
+      <c r="D24" s="104"/>
+      <c r="E24" s="104"/>
       <c r="F24" s="5" t="s">
         <v>54</v>
       </c>
@@ -4176,41 +4262,41 @@
       <c r="H24" s="2"/>
     </row>
     <row r="25" spans="1:8" ht="33.75" x14ac:dyDescent="0.6">
-      <c r="A25" s="122"/>
+      <c r="A25" s="163"/>
       <c r="B25" s="16" t="s">
         <v>9</v>
       </c>
-      <c r="C25" s="114" t="s">
+      <c r="C25" s="121" t="s">
         <v>196</v>
       </c>
-      <c r="D25" s="115"/>
-      <c r="E25" s="115"/>
+      <c r="D25" s="122"/>
+      <c r="E25" s="122"/>
       <c r="F25" s="5" t="s">
         <v>55</v>
       </c>
       <c r="G25" s="17"/>
     </row>
     <row r="26" spans="1:8" ht="105.75" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A26" s="121" t="s">
+      <c r="A26" s="162" t="s">
         <v>95</v>
       </c>
-      <c r="B26" s="126" t="s">
+      <c r="B26" s="96" t="s">
         <v>47</v>
       </c>
-      <c r="C26" s="114" t="s">
+      <c r="C26" s="121" t="s">
         <v>203</v>
       </c>
-      <c r="D26" s="115"/>
-      <c r="E26" s="130"/>
-      <c r="F26" s="138" t="s">
+      <c r="D26" s="122"/>
+      <c r="E26" s="166"/>
+      <c r="F26" s="146" t="s">
         <v>56</v>
       </c>
-      <c r="G26" s="152"/>
+      <c r="G26" s="156"/>
       <c r="H26" s="2"/>
     </row>
     <row r="27" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A27" s="122"/>
-      <c r="B27" s="127"/>
+      <c r="A27" s="163"/>
+      <c r="B27" s="165"/>
       <c r="C27" s="58" t="s">
         <v>194</v>
       </c>
@@ -4218,19 +4304,19 @@
       <c r="E27" s="60" t="s">
         <v>209</v>
       </c>
-      <c r="F27" s="139"/>
-      <c r="G27" s="153"/>
+      <c r="F27" s="147"/>
+      <c r="G27" s="157"/>
     </row>
     <row r="28" spans="1:8" ht="33.75" x14ac:dyDescent="0.6">
-      <c r="A28" s="122"/>
+      <c r="A28" s="163"/>
       <c r="B28" s="16" t="s">
         <v>10</v>
       </c>
-      <c r="C28" s="114" t="s">
+      <c r="C28" s="121" t="s">
         <v>89</v>
       </c>
-      <c r="D28" s="115"/>
-      <c r="E28" s="115"/>
+      <c r="D28" s="122"/>
+      <c r="E28" s="122"/>
       <c r="F28" s="5" t="s">
         <v>57</v>
       </c>
@@ -4238,30 +4324,30 @@
       <c r="H28" s="2"/>
     </row>
     <row r="29" spans="1:8" ht="33.75" x14ac:dyDescent="0.6">
-      <c r="A29" s="122"/>
+      <c r="A29" s="163"/>
       <c r="B29" s="31" t="s">
         <v>11</v>
       </c>
-      <c r="C29" s="140" t="s">
+      <c r="C29" s="167" t="s">
         <v>90</v>
       </c>
-      <c r="D29" s="141"/>
-      <c r="E29" s="141"/>
+      <c r="D29" s="168"/>
+      <c r="E29" s="168"/>
       <c r="F29" s="36" t="s">
         <v>91</v>
       </c>
       <c r="G29" s="32"/>
     </row>
     <row r="30" spans="1:8" ht="67.5" x14ac:dyDescent="0.6">
-      <c r="A30" s="158"/>
+      <c r="A30" s="164"/>
       <c r="B30" s="18" t="s">
         <v>92</v>
       </c>
-      <c r="C30" s="140" t="s">
+      <c r="C30" s="167" t="s">
         <v>93</v>
       </c>
-      <c r="D30" s="141"/>
-      <c r="E30" s="141"/>
+      <c r="D30" s="168"/>
+      <c r="E30" s="168"/>
       <c r="F30" s="19" t="s">
         <v>94</v>
       </c>
@@ -4273,86 +4359,86 @@
         <v>96</v>
       </c>
       <c r="B31" s="85"/>
-      <c r="C31" s="140" t="s">
+      <c r="C31" s="167" t="s">
         <v>97</v>
       </c>
-      <c r="D31" s="141"/>
-      <c r="E31" s="142"/>
+      <c r="D31" s="168"/>
+      <c r="E31" s="178"/>
       <c r="F31" s="79" t="s">
         <v>98</v>
       </c>
       <c r="G31" s="80"/>
     </row>
     <row r="32" spans="1:8" ht="50.65" x14ac:dyDescent="0.6">
-      <c r="A32" s="122" t="s">
+      <c r="A32" s="163" t="s">
         <v>99</v>
       </c>
       <c r="B32" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="C32" s="131" t="s">
+      <c r="C32" s="179" t="s">
         <v>51</v>
       </c>
-      <c r="D32" s="132"/>
-      <c r="E32" s="132"/>
+      <c r="D32" s="180"/>
+      <c r="E32" s="180"/>
       <c r="F32" s="13" t="s">
         <v>100</v>
       </c>
       <c r="G32" s="10"/>
     </row>
     <row r="33" spans="1:8" ht="33.75" x14ac:dyDescent="0.6">
-      <c r="A33" s="122"/>
+      <c r="A33" s="163"/>
       <c r="B33" s="16" t="s">
         <v>101</v>
       </c>
-      <c r="C33" s="134" t="s">
+      <c r="C33" s="103" t="s">
         <v>215</v>
       </c>
-      <c r="D33" s="135"/>
-      <c r="E33" s="135"/>
+      <c r="D33" s="104"/>
+      <c r="E33" s="104"/>
       <c r="F33" s="5" t="s">
         <v>102</v>
       </c>
       <c r="G33" s="70"/>
     </row>
     <row r="34" spans="1:8" ht="33.75" x14ac:dyDescent="0.6">
-      <c r="A34" s="122"/>
+      <c r="A34" s="163"/>
       <c r="B34" s="16" t="s">
         <v>36</v>
       </c>
-      <c r="C34" s="114" t="s">
+      <c r="C34" s="121" t="s">
         <v>37</v>
       </c>
-      <c r="D34" s="115"/>
-      <c r="E34" s="115"/>
+      <c r="D34" s="122"/>
+      <c r="E34" s="122"/>
       <c r="F34" s="5" t="s">
         <v>59</v>
       </c>
       <c r="G34" s="17"/>
     </row>
     <row r="35" spans="1:8" ht="50.65" x14ac:dyDescent="0.6">
-      <c r="A35" s="122"/>
-      <c r="B35" s="126" t="s">
+      <c r="A35" s="163"/>
+      <c r="B35" s="96" t="s">
         <v>13</v>
       </c>
-      <c r="C35" s="134" t="s">
+      <c r="C35" s="103" t="s">
         <v>216</v>
       </c>
-      <c r="D35" s="135"/>
-      <c r="E35" s="135"/>
+      <c r="D35" s="104"/>
+      <c r="E35" s="104"/>
       <c r="F35" s="27" t="s">
         <v>103</v>
       </c>
       <c r="G35" s="29"/>
     </row>
     <row r="36" spans="1:8" ht="57" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A36" s="122"/>
-      <c r="B36" s="133"/>
-      <c r="C36" s="136" t="s">
+      <c r="A36" s="163"/>
+      <c r="B36" s="97"/>
+      <c r="C36" s="141" t="s">
         <v>217</v>
       </c>
-      <c r="D36" s="137"/>
-      <c r="E36" s="137"/>
+      <c r="D36" s="142"/>
+      <c r="E36" s="142"/>
       <c r="F36" s="27" t="s">
         <v>64</v>
       </c>
@@ -4360,84 +4446,84 @@
       <c r="H36" s="2"/>
     </row>
     <row r="37" spans="1:8" ht="67.5" x14ac:dyDescent="0.6">
-      <c r="A37" s="162" t="s">
+      <c r="A37" s="196" t="s">
         <v>105</v>
       </c>
       <c r="B37" s="18" t="s">
         <v>14</v>
       </c>
-      <c r="C37" s="135" t="s">
+      <c r="C37" s="104" t="s">
         <v>106</v>
       </c>
-      <c r="D37" s="135"/>
-      <c r="E37" s="135"/>
+      <c r="D37" s="104"/>
+      <c r="E37" s="104"/>
       <c r="F37" s="5" t="s">
         <v>107</v>
       </c>
       <c r="G37" s="6"/>
     </row>
     <row r="38" spans="1:8" ht="41.25" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A38" s="162"/>
-      <c r="B38" s="163" t="s">
+      <c r="A38" s="196"/>
+      <c r="B38" s="197" t="s">
         <v>15</v>
       </c>
-      <c r="C38" s="164" t="s">
+      <c r="C38" s="198" t="s">
         <v>197</v>
       </c>
-      <c r="D38" s="164"/>
-      <c r="E38" s="164"/>
-      <c r="F38" s="181" t="s">
+      <c r="D38" s="198"/>
+      <c r="E38" s="198"/>
+      <c r="F38" s="144" t="s">
         <v>62</v>
       </c>
-      <c r="G38" s="175"/>
+      <c r="G38" s="130"/>
     </row>
     <row r="39" spans="1:8" ht="32.25" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A39" s="162"/>
-      <c r="B39" s="163"/>
+      <c r="A39" s="196"/>
+      <c r="B39" s="197"/>
       <c r="C39" s="86" t="s">
         <v>108</v>
       </c>
-      <c r="D39" s="108"/>
-      <c r="E39" s="109"/>
-      <c r="F39" s="182"/>
-      <c r="G39" s="175"/>
+      <c r="D39" s="194"/>
+      <c r="E39" s="195"/>
+      <c r="F39" s="145"/>
+      <c r="G39" s="130"/>
     </row>
     <row r="40" spans="1:8" ht="23.25" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A40" s="162"/>
-      <c r="B40" s="176" t="s">
+      <c r="A40" s="196"/>
+      <c r="B40" s="131" t="s">
         <v>16</v>
       </c>
-      <c r="C40" s="135" t="s">
+      <c r="C40" s="104" t="s">
         <v>42</v>
       </c>
-      <c r="D40" s="135"/>
-      <c r="E40" s="135"/>
-      <c r="F40" s="138" t="s">
+      <c r="D40" s="104"/>
+      <c r="E40" s="104"/>
+      <c r="F40" s="146" t="s">
         <v>63</v>
       </c>
-      <c r="G40" s="143"/>
+      <c r="G40" s="132"/>
     </row>
     <row r="41" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A41" s="162"/>
-      <c r="B41" s="176"/>
+      <c r="A41" s="196"/>
+      <c r="B41" s="131"/>
       <c r="C41" s="61" t="s">
         <v>109</v>
       </c>
-      <c r="D41" s="183"/>
-      <c r="E41" s="184"/>
-      <c r="F41" s="139"/>
-      <c r="G41" s="143"/>
+      <c r="D41" s="148"/>
+      <c r="E41" s="149"/>
+      <c r="F41" s="147"/>
+      <c r="G41" s="132"/>
     </row>
     <row r="42" spans="1:8" ht="53.25" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A42" s="162"/>
+      <c r="A42" s="196"/>
       <c r="B42" s="31" t="s">
         <v>110</v>
       </c>
-      <c r="C42" s="136" t="s">
+      <c r="C42" s="141" t="s">
         <v>204</v>
       </c>
-      <c r="D42" s="137"/>
-      <c r="E42" s="180"/>
+      <c r="D42" s="142"/>
+      <c r="E42" s="143"/>
       <c r="F42" s="27" t="s">
         <v>64</v>
       </c>
@@ -4445,107 +4531,107 @@
       <c r="H42" s="2"/>
     </row>
     <row r="43" spans="1:8" ht="158.25" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A43" s="177" t="s">
+      <c r="A43" s="135" t="s">
         <v>111</v>
       </c>
       <c r="B43" s="33" t="s">
         <v>112</v>
       </c>
-      <c r="C43" s="165" t="s">
+      <c r="C43" s="138" t="s">
         <v>198</v>
       </c>
-      <c r="D43" s="166"/>
-      <c r="E43" s="167"/>
+      <c r="D43" s="139"/>
+      <c r="E43" s="140"/>
       <c r="F43" s="35" t="s">
         <v>113</v>
       </c>
       <c r="G43" s="29"/>
     </row>
     <row r="44" spans="1:8" ht="33.75" x14ac:dyDescent="0.6">
-      <c r="A44" s="178"/>
+      <c r="A44" s="136"/>
       <c r="B44" s="33" t="s">
         <v>114</v>
       </c>
-      <c r="C44" s="165" t="s">
+      <c r="C44" s="138" t="s">
         <v>121</v>
       </c>
-      <c r="D44" s="166"/>
-      <c r="E44" s="167"/>
+      <c r="D44" s="139"/>
+      <c r="E44" s="140"/>
       <c r="F44" s="35" t="s">
         <v>122</v>
       </c>
       <c r="G44" s="29"/>
     </row>
     <row r="45" spans="1:8" ht="33.75" x14ac:dyDescent="0.6">
-      <c r="A45" s="178"/>
+      <c r="A45" s="136"/>
       <c r="B45" s="33" t="s">
         <v>115</v>
       </c>
-      <c r="C45" s="165" t="s">
+      <c r="C45" s="138" t="s">
         <v>218</v>
       </c>
-      <c r="D45" s="166"/>
-      <c r="E45" s="167"/>
+      <c r="D45" s="139"/>
+      <c r="E45" s="140"/>
       <c r="F45" s="35" t="s">
         <v>123</v>
       </c>
       <c r="G45" s="29"/>
     </row>
     <row r="46" spans="1:8" ht="33.75" x14ac:dyDescent="0.6">
-      <c r="A46" s="178"/>
+      <c r="A46" s="136"/>
       <c r="B46" s="33" t="s">
         <v>116</v>
       </c>
-      <c r="C46" s="165" t="s">
+      <c r="C46" s="138" t="s">
         <v>124</v>
       </c>
-      <c r="D46" s="166"/>
-      <c r="E46" s="167"/>
+      <c r="D46" s="139"/>
+      <c r="E46" s="140"/>
       <c r="F46" s="35" t="s">
         <v>125</v>
       </c>
       <c r="G46" s="29"/>
     </row>
     <row r="47" spans="1:8" ht="33.75" x14ac:dyDescent="0.6">
-      <c r="A47" s="178"/>
+      <c r="A47" s="136"/>
       <c r="B47" s="33" t="s">
         <v>117</v>
       </c>
-      <c r="C47" s="165" t="s">
+      <c r="C47" s="138" t="s">
         <v>126</v>
       </c>
-      <c r="D47" s="166"/>
-      <c r="E47" s="167"/>
+      <c r="D47" s="139"/>
+      <c r="E47" s="140"/>
       <c r="F47" s="35" t="s">
         <v>127</v>
       </c>
       <c r="G47" s="29"/>
     </row>
     <row r="48" spans="1:8" ht="33.75" x14ac:dyDescent="0.6">
-      <c r="A48" s="179"/>
+      <c r="A48" s="137"/>
       <c r="B48" s="33" t="s">
         <v>118</v>
       </c>
-      <c r="C48" s="165" t="s">
+      <c r="C48" s="138" t="s">
         <v>128</v>
       </c>
-      <c r="D48" s="166"/>
-      <c r="E48" s="167"/>
+      <c r="D48" s="139"/>
+      <c r="E48" s="140"/>
       <c r="F48" s="35" t="s">
         <v>129</v>
       </c>
       <c r="G48" s="29"/>
     </row>
     <row r="49" spans="1:8" ht="34.15" thickBot="1" x14ac:dyDescent="0.65">
-      <c r="A49" s="185" t="s">
+      <c r="A49" s="150" t="s">
         <v>119</v>
       </c>
-      <c r="B49" s="186"/>
-      <c r="C49" s="187" t="s">
+      <c r="B49" s="151"/>
+      <c r="C49" s="152" t="s">
         <v>120</v>
       </c>
-      <c r="D49" s="187"/>
-      <c r="E49" s="188"/>
+      <c r="D49" s="152"/>
+      <c r="E49" s="153"/>
       <c r="F49" s="14" t="s">
         <v>176</v>
       </c>
@@ -4558,95 +4644,95 @@
       </c>
     </row>
     <row r="52" spans="1:8" ht="17.25" thickTop="1" x14ac:dyDescent="0.6">
-      <c r="A52" s="122" t="s">
+      <c r="A52" s="163" t="s">
         <v>132</v>
       </c>
-      <c r="B52" s="189" t="s">
+      <c r="B52" s="154" t="s">
         <v>18</v>
       </c>
-      <c r="C52" s="156" t="s">
+      <c r="C52" s="160" t="s">
         <v>130</v>
       </c>
-      <c r="D52" s="157"/>
-      <c r="E52" s="157"/>
+      <c r="D52" s="161"/>
+      <c r="E52" s="161"/>
       <c r="F52" s="11" t="s">
         <v>43</v>
       </c>
       <c r="G52" s="4"/>
     </row>
     <row r="53" spans="1:8" ht="53.25" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A53" s="122"/>
-      <c r="B53" s="133"/>
-      <c r="C53" s="140" t="s">
+      <c r="A53" s="163"/>
+      <c r="B53" s="97"/>
+      <c r="C53" s="167" t="s">
         <v>195</v>
       </c>
-      <c r="D53" s="141"/>
-      <c r="E53" s="141"/>
+      <c r="D53" s="168"/>
+      <c r="E53" s="168"/>
       <c r="F53" s="18" t="s">
         <v>43</v>
       </c>
       <c r="G53" s="72"/>
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.6">
-      <c r="A54" s="122"/>
-      <c r="B54" s="133"/>
-      <c r="C54" s="140" t="s">
+      <c r="A54" s="163"/>
+      <c r="B54" s="97"/>
+      <c r="C54" s="167" t="s">
         <v>44</v>
       </c>
-      <c r="D54" s="141"/>
-      <c r="E54" s="141"/>
+      <c r="D54" s="168"/>
+      <c r="E54" s="168"/>
       <c r="F54" s="18" t="s">
         <v>43</v>
       </c>
       <c r="G54" s="4"/>
     </row>
     <row r="55" spans="1:8" ht="33.75" x14ac:dyDescent="0.6">
-      <c r="A55" s="122"/>
-      <c r="B55" s="133"/>
-      <c r="C55" s="134" t="s">
+      <c r="A55" s="163"/>
+      <c r="B55" s="97"/>
+      <c r="C55" s="103" t="s">
         <v>205</v>
       </c>
-      <c r="D55" s="135"/>
-      <c r="E55" s="135"/>
+      <c r="D55" s="104"/>
+      <c r="E55" s="104"/>
       <c r="F55" s="5" t="s">
         <v>131</v>
       </c>
       <c r="G55" s="6"/>
     </row>
     <row r="56" spans="1:8" ht="102.75" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A56" s="122"/>
-      <c r="B56" s="133"/>
-      <c r="C56" s="134" t="s">
+      <c r="A56" s="163"/>
+      <c r="B56" s="97"/>
+      <c r="C56" s="103" t="s">
         <v>133</v>
       </c>
-      <c r="D56" s="135"/>
-      <c r="E56" s="168"/>
+      <c r="D56" s="104"/>
+      <c r="E56" s="111"/>
       <c r="F56" s="27" t="s">
         <v>48</v>
       </c>
       <c r="G56" s="29"/>
     </row>
     <row r="57" spans="1:8" ht="84" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A57" s="122"/>
-      <c r="B57" s="133"/>
-      <c r="C57" s="134" t="s">
+      <c r="A57" s="163"/>
+      <c r="B57" s="97"/>
+      <c r="C57" s="103" t="s">
         <v>135</v>
       </c>
-      <c r="D57" s="135"/>
-      <c r="E57" s="168"/>
+      <c r="D57" s="104"/>
+      <c r="E57" s="111"/>
       <c r="F57" s="27" t="s">
         <v>136</v>
       </c>
       <c r="G57" s="67"/>
     </row>
     <row r="58" spans="1:8" ht="118.15" x14ac:dyDescent="0.6">
-      <c r="A58" s="122"/>
-      <c r="B58" s="133"/>
-      <c r="C58" s="119" t="s">
+      <c r="A58" s="163"/>
+      <c r="B58" s="97"/>
+      <c r="C58" s="133" t="s">
         <v>137</v>
       </c>
-      <c r="D58" s="120"/>
-      <c r="E58" s="190"/>
+      <c r="D58" s="134"/>
+      <c r="E58" s="155"/>
       <c r="F58" s="40" t="s">
         <v>138</v>
       </c>
@@ -4654,28 +4740,28 @@
       <c r="H58" s="2"/>
     </row>
     <row r="59" spans="1:8" ht="33.75" x14ac:dyDescent="0.6">
-      <c r="A59" s="122"/>
-      <c r="B59" s="133"/>
-      <c r="C59" s="134" t="s">
+      <c r="A59" s="163"/>
+      <c r="B59" s="97"/>
+      <c r="C59" s="103" t="s">
         <v>139</v>
       </c>
-      <c r="D59" s="135"/>
-      <c r="E59" s="168"/>
+      <c r="D59" s="104"/>
+      <c r="E59" s="111"/>
       <c r="F59" s="27" t="s">
         <v>140</v>
       </c>
       <c r="G59" s="29"/>
     </row>
     <row r="60" spans="1:8" ht="102" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A60" s="122"/>
+      <c r="A60" s="163"/>
       <c r="B60" s="16" t="s">
         <v>141</v>
       </c>
-      <c r="C60" s="169" t="s">
+      <c r="C60" s="199" t="s">
         <v>142</v>
       </c>
-      <c r="D60" s="170"/>
-      <c r="E60" s="170"/>
+      <c r="D60" s="200"/>
+      <c r="E60" s="200"/>
       <c r="F60" s="64" t="s">
         <v>144</v>
       </c>
@@ -4686,11 +4772,11 @@
         <v>145</v>
       </c>
       <c r="B61" s="76"/>
-      <c r="C61" s="119" t="s">
+      <c r="C61" s="133" t="s">
         <v>199</v>
       </c>
-      <c r="D61" s="120"/>
-      <c r="E61" s="120"/>
+      <c r="D61" s="134"/>
+      <c r="E61" s="134"/>
       <c r="F61" s="27" t="s">
         <v>134</v>
       </c>
@@ -4702,39 +4788,39 @@
         <v>146</v>
       </c>
       <c r="B62" s="76"/>
-      <c r="C62" s="119" t="s">
+      <c r="C62" s="133" t="s">
         <v>150</v>
       </c>
-      <c r="D62" s="120"/>
-      <c r="E62" s="120"/>
+      <c r="D62" s="134"/>
+      <c r="E62" s="134"/>
       <c r="F62" s="27" t="s">
         <v>151</v>
       </c>
       <c r="G62" s="32"/>
     </row>
     <row r="63" spans="1:8" ht="108" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A63" s="106" t="s">
+      <c r="A63" s="102" t="s">
         <v>147</v>
       </c>
       <c r="B63" s="76"/>
-      <c r="C63" s="134" t="s">
+      <c r="C63" s="103" t="s">
         <v>148</v>
       </c>
-      <c r="D63" s="135"/>
-      <c r="E63" s="135"/>
+      <c r="D63" s="104"/>
+      <c r="E63" s="104"/>
       <c r="F63" s="64" t="s">
         <v>152</v>
       </c>
       <c r="G63" s="32"/>
     </row>
     <row r="64" spans="1:8" x14ac:dyDescent="0.6">
-      <c r="A64" s="107"/>
+      <c r="A64" s="193"/>
       <c r="B64" s="76"/>
-      <c r="C64" s="112" t="s">
+      <c r="C64" s="119" t="s">
         <v>149</v>
       </c>
-      <c r="D64" s="113"/>
-      <c r="E64" s="151"/>
+      <c r="D64" s="120"/>
+      <c r="E64" s="126"/>
       <c r="F64" s="64" t="s">
         <v>143</v>
       </c>
@@ -4745,263 +4831,263 @@
         <v>153</v>
       </c>
       <c r="B65" s="76"/>
-      <c r="C65" s="134" t="s">
+      <c r="C65" s="103" t="s">
         <v>155</v>
       </c>
-      <c r="D65" s="135"/>
-      <c r="E65" s="135"/>
+      <c r="D65" s="104"/>
+      <c r="E65" s="104"/>
       <c r="F65" s="27" t="s">
         <v>104</v>
       </c>
       <c r="G65" s="32"/>
     </row>
     <row r="66" spans="1:7" ht="51.75" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A66" s="121" t="s">
+      <c r="A66" s="162" t="s">
         <v>154</v>
       </c>
       <c r="B66" s="34" t="s">
         <v>19</v>
       </c>
-      <c r="C66" s="123" t="s">
+      <c r="C66" s="181" t="s">
         <v>219</v>
       </c>
-      <c r="D66" s="124"/>
-      <c r="E66" s="125"/>
+      <c r="D66" s="182"/>
+      <c r="E66" s="183"/>
       <c r="F66" s="5" t="s">
         <v>65</v>
       </c>
       <c r="G66" s="17"/>
     </row>
     <row r="67" spans="1:7" ht="33.75" x14ac:dyDescent="0.6">
-      <c r="A67" s="122"/>
-      <c r="B67" s="126" t="s">
+      <c r="A67" s="163"/>
+      <c r="B67" s="96" t="s">
         <v>32</v>
       </c>
-      <c r="C67" s="128" t="s">
+      <c r="C67" s="184" t="s">
         <v>220</v>
       </c>
-      <c r="D67" s="129"/>
-      <c r="E67" s="129"/>
+      <c r="D67" s="185"/>
+      <c r="E67" s="185"/>
       <c r="F67" s="62" t="s">
         <v>157</v>
       </c>
       <c r="G67" s="65"/>
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.6">
-      <c r="A68" s="122"/>
-      <c r="B68" s="127"/>
-      <c r="C68" s="140" t="s">
+      <c r="A68" s="163"/>
+      <c r="B68" s="165"/>
+      <c r="C68" s="167" t="s">
         <v>156</v>
       </c>
-      <c r="D68" s="141"/>
-      <c r="E68" s="171"/>
+      <c r="D68" s="168"/>
+      <c r="E68" s="201"/>
       <c r="F68" s="20" t="s">
         <v>43</v>
       </c>
       <c r="G68" s="12"/>
     </row>
     <row r="69" spans="1:7" ht="33.75" x14ac:dyDescent="0.6">
-      <c r="A69" s="122"/>
-      <c r="B69" s="126" t="s">
+      <c r="A69" s="163"/>
+      <c r="B69" s="96" t="s">
         <v>20</v>
       </c>
-      <c r="C69" s="128" t="s">
+      <c r="C69" s="184" t="s">
         <v>158</v>
       </c>
-      <c r="D69" s="129"/>
-      <c r="E69" s="129"/>
+      <c r="D69" s="185"/>
+      <c r="E69" s="185"/>
       <c r="F69" s="63" t="s">
         <v>159</v>
       </c>
       <c r="G69" s="65"/>
     </row>
     <row r="70" spans="1:7" ht="33.75" x14ac:dyDescent="0.6">
-      <c r="A70" s="122"/>
-      <c r="B70" s="127"/>
-      <c r="C70" s="172" t="s">
+      <c r="A70" s="163"/>
+      <c r="B70" s="165"/>
+      <c r="C70" s="127" t="s">
         <v>160</v>
       </c>
-      <c r="D70" s="173"/>
-      <c r="E70" s="174"/>
+      <c r="D70" s="128"/>
+      <c r="E70" s="129"/>
       <c r="F70" s="28" t="s">
         <v>161</v>
       </c>
       <c r="G70" s="30"/>
     </row>
     <row r="71" spans="1:7" ht="33.75" x14ac:dyDescent="0.6">
-      <c r="A71" s="122"/>
+      <c r="A71" s="163"/>
       <c r="B71" s="16" t="s">
         <v>21</v>
       </c>
-      <c r="C71" s="134" t="s">
+      <c r="C71" s="103" t="s">
         <v>162</v>
       </c>
-      <c r="D71" s="135"/>
-      <c r="E71" s="135"/>
+      <c r="D71" s="104"/>
+      <c r="E71" s="104"/>
       <c r="F71" s="5" t="s">
         <v>49</v>
       </c>
       <c r="G71" s="6"/>
     </row>
     <row r="72" spans="1:7" ht="33.75" x14ac:dyDescent="0.6">
-      <c r="A72" s="121" t="s">
+      <c r="A72" s="162" t="s">
         <v>163</v>
       </c>
       <c r="B72" s="16" t="s">
         <v>8</v>
       </c>
-      <c r="C72" s="134" t="s">
+      <c r="C72" s="103" t="s">
         <v>164</v>
       </c>
-      <c r="D72" s="135"/>
-      <c r="E72" s="135"/>
+      <c r="D72" s="104"/>
+      <c r="E72" s="104"/>
       <c r="F72" s="5" t="s">
         <v>66</v>
       </c>
       <c r="G72" s="6"/>
     </row>
     <row r="73" spans="1:7" ht="33.75" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A73" s="122"/>
+      <c r="A73" s="163"/>
       <c r="B73" s="34" t="s">
         <v>22</v>
       </c>
-      <c r="C73" s="114" t="s">
+      <c r="C73" s="121" t="s">
         <v>165</v>
       </c>
-      <c r="D73" s="115"/>
-      <c r="E73" s="115"/>
+      <c r="D73" s="122"/>
+      <c r="E73" s="122"/>
       <c r="F73" s="27" t="s">
         <v>58</v>
       </c>
       <c r="G73" s="32"/>
     </row>
     <row r="74" spans="1:7" ht="33.75" x14ac:dyDescent="0.6">
-      <c r="A74" s="122"/>
-      <c r="B74" s="126" t="s">
+      <c r="A74" s="163"/>
+      <c r="B74" s="96" t="s">
         <v>23</v>
       </c>
-      <c r="C74" s="134" t="s">
+      <c r="C74" s="103" t="s">
         <v>166</v>
       </c>
-      <c r="D74" s="135"/>
-      <c r="E74" s="135"/>
+      <c r="D74" s="104"/>
+      <c r="E74" s="104"/>
       <c r="F74" s="5" t="s">
         <v>67</v>
       </c>
       <c r="G74" s="6"/>
     </row>
     <row r="75" spans="1:7" ht="37.5" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A75" s="122"/>
-      <c r="B75" s="133"/>
-      <c r="C75" s="114" t="s">
+      <c r="A75" s="163"/>
+      <c r="B75" s="97"/>
+      <c r="C75" s="121" t="s">
         <v>206</v>
       </c>
-      <c r="D75" s="115"/>
-      <c r="E75" s="130"/>
+      <c r="D75" s="122"/>
+      <c r="E75" s="166"/>
       <c r="F75" s="27" t="s">
         <v>68</v>
       </c>
       <c r="G75" s="29"/>
     </row>
     <row r="76" spans="1:7" ht="33.75" x14ac:dyDescent="0.6">
-      <c r="A76" s="122"/>
-      <c r="B76" s="126" t="s">
+      <c r="A76" s="163"/>
+      <c r="B76" s="96" t="s">
         <v>24</v>
       </c>
-      <c r="C76" s="134" t="s">
+      <c r="C76" s="103" t="s">
         <v>167</v>
       </c>
-      <c r="D76" s="135"/>
-      <c r="E76" s="135"/>
+      <c r="D76" s="104"/>
+      <c r="E76" s="104"/>
       <c r="F76" s="19" t="s">
         <v>58</v>
       </c>
       <c r="G76" s="6"/>
     </row>
     <row r="77" spans="1:7" ht="33.75" x14ac:dyDescent="0.6">
-      <c r="A77" s="161"/>
-      <c r="B77" s="133"/>
-      <c r="C77" s="134" t="s">
+      <c r="A77" s="186"/>
+      <c r="B77" s="97"/>
+      <c r="C77" s="103" t="s">
         <v>200</v>
       </c>
-      <c r="D77" s="135"/>
-      <c r="E77" s="135"/>
+      <c r="D77" s="104"/>
+      <c r="E77" s="104"/>
       <c r="F77" s="5" t="s">
         <v>69</v>
       </c>
       <c r="G77" s="6"/>
     </row>
     <row r="78" spans="1:7" ht="33.75" x14ac:dyDescent="0.6">
-      <c r="A78" s="196" t="s">
+      <c r="A78" s="95" t="s">
         <v>168</v>
       </c>
-      <c r="B78" s="126" t="s">
+      <c r="B78" s="96" t="s">
         <v>38</v>
       </c>
-      <c r="C78" s="197" t="s">
+      <c r="C78" s="98" t="s">
         <v>169</v>
       </c>
-      <c r="D78" s="198"/>
-      <c r="E78" s="198"/>
+      <c r="D78" s="99"/>
+      <c r="E78" s="99"/>
       <c r="F78" s="68" t="s">
         <v>208</v>
       </c>
       <c r="G78" s="69"/>
     </row>
     <row r="79" spans="1:7" ht="33.75" x14ac:dyDescent="0.6">
-      <c r="A79" s="196"/>
-      <c r="B79" s="133"/>
-      <c r="C79" s="199" t="s">
+      <c r="A79" s="95"/>
+      <c r="B79" s="97"/>
+      <c r="C79" s="100" t="s">
         <v>70</v>
       </c>
-      <c r="D79" s="200"/>
-      <c r="E79" s="200"/>
+      <c r="D79" s="101"/>
+      <c r="E79" s="101"/>
       <c r="F79" s="68" t="s">
         <v>208</v>
       </c>
       <c r="G79" s="69"/>
     </row>
     <row r="80" spans="1:7" ht="33.75" x14ac:dyDescent="0.6">
-      <c r="A80" s="106" t="s">
+      <c r="A80" s="89" t="s">
         <v>25</v>
       </c>
-      <c r="B80" s="201"/>
-      <c r="C80" s="134" t="s">
+      <c r="B80" s="205"/>
+      <c r="C80" s="103" t="s">
         <v>207</v>
       </c>
-      <c r="D80" s="135"/>
-      <c r="E80" s="135"/>
+      <c r="D80" s="104"/>
+      <c r="E80" s="104"/>
       <c r="F80" s="5" t="s">
         <v>58</v>
       </c>
       <c r="G80" s="21"/>
     </row>
     <row r="81" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A81" s="202" t="s">
+      <c r="A81" s="105" t="s">
         <v>33</v>
       </c>
       <c r="B81" s="22" t="s">
         <v>26</v>
       </c>
-      <c r="C81" s="204" t="s">
+      <c r="C81" s="107" t="s">
         <v>213</v>
       </c>
-      <c r="D81" s="205"/>
-      <c r="E81" s="205"/>
+      <c r="D81" s="108"/>
+      <c r="E81" s="108"/>
       <c r="F81" s="22">
         <v>3</v>
       </c>
       <c r="G81" s="23"/>
     </row>
     <row r="82" spans="1:8" ht="22.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.65">
-      <c r="A82" s="203"/>
+      <c r="A82" s="106"/>
       <c r="B82" s="24" t="s">
         <v>27</v>
       </c>
-      <c r="C82" s="206" t="s">
+      <c r="C82" s="109" t="s">
         <v>212</v>
       </c>
-      <c r="D82" s="207"/>
+      <c r="D82" s="110"/>
       <c r="E82" s="25"/>
       <c r="F82" s="24">
         <v>2</v>
@@ -5016,15 +5102,15 @@
       <c r="B84" s="1"/>
     </row>
     <row r="85" spans="1:8" ht="24" customHeight="1" thickTop="1" x14ac:dyDescent="0.6">
-      <c r="A85" s="98" t="s">
+      <c r="A85" s="93" t="s">
         <v>29</v>
       </c>
-      <c r="B85" s="89"/>
-      <c r="C85" s="110" t="s">
+      <c r="B85" s="202"/>
+      <c r="C85" s="117" t="s">
         <v>34</v>
       </c>
-      <c r="D85" s="111"/>
-      <c r="E85" s="111"/>
+      <c r="D85" s="118"/>
+      <c r="E85" s="118"/>
       <c r="F85" s="11">
         <v>5</v>
       </c>
@@ -5034,12 +5120,12 @@
       <c r="A86" s="82" t="s">
         <v>171</v>
       </c>
-      <c r="B86" s="90"/>
-      <c r="C86" s="112" t="s">
+      <c r="B86" s="203"/>
+      <c r="C86" s="119" t="s">
         <v>172</v>
       </c>
-      <c r="D86" s="113"/>
-      <c r="E86" s="113"/>
+      <c r="D86" s="120"/>
+      <c r="E86" s="120"/>
       <c r="F86" s="18">
         <v>5</v>
       </c>
@@ -5049,12 +5135,12 @@
       <c r="A87" s="82" t="s">
         <v>45</v>
       </c>
-      <c r="B87" s="90"/>
-      <c r="C87" s="112" t="s">
+      <c r="B87" s="203"/>
+      <c r="C87" s="119" t="s">
         <v>173</v>
       </c>
-      <c r="D87" s="113"/>
-      <c r="E87" s="113"/>
+      <c r="D87" s="120"/>
+      <c r="E87" s="120"/>
       <c r="F87" s="18">
         <v>5</v>
       </c>
@@ -5064,12 +5150,12 @@
       <c r="A88" s="82" t="s">
         <v>30</v>
       </c>
-      <c r="B88" s="90"/>
-      <c r="C88" s="112" t="s">
+      <c r="B88" s="203"/>
+      <c r="C88" s="119" t="s">
         <v>35</v>
       </c>
-      <c r="D88" s="113"/>
-      <c r="E88" s="113"/>
+      <c r="D88" s="120"/>
+      <c r="E88" s="120"/>
       <c r="F88" s="31">
         <v>5</v>
       </c>
@@ -5079,27 +5165,27 @@
       <c r="A89" s="82" t="s">
         <v>31</v>
       </c>
-      <c r="B89" s="90"/>
-      <c r="C89" s="114" t="s">
+      <c r="B89" s="203"/>
+      <c r="C89" s="121" t="s">
         <v>174</v>
       </c>
-      <c r="D89" s="115"/>
-      <c r="E89" s="115"/>
+      <c r="D89" s="122"/>
+      <c r="E89" s="122"/>
       <c r="F89" s="34">
         <v>5</v>
       </c>
       <c r="G89" s="41"/>
     </row>
     <row r="90" spans="1:8" ht="74.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.65">
-      <c r="A90" s="99" t="s">
+      <c r="A90" s="94" t="s">
         <v>175</v>
       </c>
-      <c r="B90" s="97"/>
-      <c r="C90" s="116" t="s">
+      <c r="B90" s="204"/>
+      <c r="C90" s="123" t="s">
         <v>214</v>
       </c>
-      <c r="D90" s="117"/>
-      <c r="E90" s="118"/>
+      <c r="D90" s="124"/>
+      <c r="E90" s="125"/>
       <c r="F90" s="42">
         <v>10</v>
       </c>
@@ -5122,105 +5208,105 @@
       <c r="B92" s="1"/>
     </row>
     <row r="93" spans="1:8" ht="39" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A93" s="93" t="s">
+      <c r="A93" s="90" t="s">
         <v>222</v>
       </c>
-      <c r="B93" s="94"/>
-      <c r="C93" s="110" t="s">
+      <c r="B93" s="206"/>
+      <c r="C93" s="117" t="s">
         <v>228</v>
       </c>
-      <c r="D93" s="111"/>
-      <c r="E93" s="111"/>
+      <c r="D93" s="118"/>
+      <c r="E93" s="118"/>
       <c r="F93" s="73" t="s">
         <v>64</v>
       </c>
       <c r="G93" s="74"/>
     </row>
     <row r="94" spans="1:8" ht="39" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A94" s="95" t="s">
+      <c r="A94" s="91" t="s">
         <v>223</v>
       </c>
-      <c r="B94" s="90"/>
-      <c r="C94" s="112" t="s">
+      <c r="B94" s="203"/>
+      <c r="C94" s="119" t="s">
         <v>229</v>
       </c>
-      <c r="D94" s="113"/>
-      <c r="E94" s="113"/>
+      <c r="D94" s="120"/>
+      <c r="E94" s="120"/>
       <c r="F94" s="73" t="s">
         <v>64</v>
       </c>
       <c r="G94" s="74"/>
     </row>
     <row r="95" spans="1:8" ht="129.75" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A95" s="95" t="s">
+      <c r="A95" s="91" t="s">
         <v>224</v>
       </c>
-      <c r="B95" s="90"/>
-      <c r="C95" s="112" t="s">
+      <c r="B95" s="203"/>
+      <c r="C95" s="119" t="s">
         <v>230</v>
       </c>
-      <c r="D95" s="113"/>
-      <c r="E95" s="113"/>
+      <c r="D95" s="120"/>
+      <c r="E95" s="120"/>
       <c r="F95" s="73" t="s">
         <v>64</v>
       </c>
       <c r="G95" s="74"/>
     </row>
     <row r="96" spans="1:8" ht="49.5" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A96" s="95" t="s">
+      <c r="A96" s="91" t="s">
         <v>225</v>
       </c>
-      <c r="B96" s="90"/>
-      <c r="C96" s="112" t="s">
+      <c r="B96" s="203"/>
+      <c r="C96" s="119" t="s">
         <v>231</v>
       </c>
-      <c r="D96" s="113"/>
-      <c r="E96" s="151"/>
+      <c r="D96" s="120"/>
+      <c r="E96" s="126"/>
       <c r="F96" s="73" t="s">
         <v>64</v>
       </c>
       <c r="G96" s="75"/>
     </row>
     <row r="97" spans="1:8" ht="122.25" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A97" s="95" t="s">
+      <c r="A97" s="91" t="s">
         <v>226</v>
       </c>
-      <c r="B97" s="90"/>
-      <c r="C97" s="112" t="s">
+      <c r="B97" s="203"/>
+      <c r="C97" s="119" t="s">
         <v>192</v>
       </c>
-      <c r="D97" s="113"/>
-      <c r="E97" s="151"/>
+      <c r="D97" s="120"/>
+      <c r="E97" s="126"/>
       <c r="F97" s="73" t="s">
         <v>64</v>
       </c>
       <c r="G97" s="30"/>
     </row>
     <row r="98" spans="1:8" ht="38.25" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A98" s="92" t="s">
+      <c r="A98" s="89" t="s">
         <v>227</v>
       </c>
-      <c r="B98" s="91"/>
-      <c r="C98" s="114" t="s">
+      <c r="B98" s="207"/>
+      <c r="C98" s="121" t="s">
         <v>232</v>
       </c>
-      <c r="D98" s="115"/>
-      <c r="E98" s="115"/>
+      <c r="D98" s="122"/>
+      <c r="E98" s="122"/>
       <c r="F98" s="73" t="s">
         <v>64</v>
       </c>
       <c r="G98" s="41"/>
     </row>
     <row r="99" spans="1:8" ht="36.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.65">
-      <c r="A99" s="96" t="s">
+      <c r="A99" s="92" t="s">
         <v>141</v>
       </c>
-      <c r="B99" s="97"/>
-      <c r="C99" s="116" t="s">
+      <c r="B99" s="204"/>
+      <c r="C99" s="123" t="s">
         <v>233</v>
       </c>
-      <c r="D99" s="117"/>
-      <c r="E99" s="118"/>
+      <c r="D99" s="124"/>
+      <c r="E99" s="125"/>
       <c r="F99" s="88" t="s">
         <v>64</v>
       </c>
@@ -5246,12 +5332,12 @@
       <c r="A103" s="49" t="s">
         <v>1</v>
       </c>
-      <c r="B103" s="193" t="s">
+      <c r="B103" s="114" t="s">
         <v>2</v>
       </c>
-      <c r="C103" s="193"/>
-      <c r="D103" s="193"/>
-      <c r="E103" s="193"/>
+      <c r="C103" s="114"/>
+      <c r="D103" s="114"/>
+      <c r="E103" s="114"/>
       <c r="F103" s="50" t="s">
         <v>39</v>
       </c>
@@ -5263,12 +5349,12 @@
       <c r="A104" s="47" t="s">
         <v>190</v>
       </c>
-      <c r="B104" s="194" t="s">
+      <c r="B104" s="115" t="s">
         <v>188</v>
       </c>
-      <c r="C104" s="194"/>
-      <c r="D104" s="194"/>
-      <c r="E104" s="194"/>
+      <c r="C104" s="115"/>
+      <c r="D104" s="115"/>
+      <c r="E104" s="115"/>
       <c r="F104" s="48" t="s">
         <v>64</v>
       </c>
@@ -5280,12 +5366,12 @@
       <c r="A105" s="45" t="s">
         <v>178</v>
       </c>
-      <c r="B105" s="192" t="s">
+      <c r="B105" s="113" t="s">
         <v>179</v>
       </c>
-      <c r="C105" s="192"/>
-      <c r="D105" s="192"/>
-      <c r="E105" s="192"/>
+      <c r="C105" s="113"/>
+      <c r="D105" s="113"/>
+      <c r="E105" s="113"/>
       <c r="F105" s="44" t="s">
         <v>64</v>
       </c>
@@ -5297,12 +5383,12 @@
       <c r="A106" s="45" t="s">
         <v>14</v>
       </c>
-      <c r="B106" s="192" t="s">
+      <c r="B106" s="113" t="s">
         <v>191</v>
       </c>
-      <c r="C106" s="192"/>
-      <c r="D106" s="192"/>
-      <c r="E106" s="192"/>
+      <c r="C106" s="113"/>
+      <c r="D106" s="113"/>
+      <c r="E106" s="113"/>
       <c r="F106" s="44" t="s">
         <v>65</v>
       </c>
@@ -5314,12 +5400,12 @@
       <c r="A107" s="45" t="s">
         <v>180</v>
       </c>
-      <c r="B107" s="192" t="s">
+      <c r="B107" s="113" t="s">
         <v>181</v>
       </c>
-      <c r="C107" s="192"/>
-      <c r="D107" s="192"/>
-      <c r="E107" s="192"/>
+      <c r="C107" s="113"/>
+      <c r="D107" s="113"/>
+      <c r="E107" s="113"/>
       <c r="F107" s="44" t="s">
         <v>64</v>
       </c>
@@ -5331,12 +5417,12 @@
       <c r="A108" s="45" t="s">
         <v>182</v>
       </c>
-      <c r="B108" s="192" t="s">
+      <c r="B108" s="113" t="s">
         <v>192</v>
       </c>
-      <c r="C108" s="192"/>
-      <c r="D108" s="192"/>
-      <c r="E108" s="192"/>
+      <c r="C108" s="113"/>
+      <c r="D108" s="113"/>
+      <c r="E108" s="113"/>
       <c r="F108" s="44" t="s">
         <v>104</v>
       </c>
@@ -5348,12 +5434,12 @@
       <c r="A109" s="45" t="s">
         <v>183</v>
       </c>
-      <c r="B109" s="192" t="s">
+      <c r="B109" s="113" t="s">
         <v>184</v>
       </c>
-      <c r="C109" s="192"/>
-      <c r="D109" s="192"/>
-      <c r="E109" s="192"/>
+      <c r="C109" s="113"/>
+      <c r="D109" s="113"/>
+      <c r="E109" s="113"/>
       <c r="F109" s="44" t="s">
         <v>64</v>
       </c>
@@ -5365,12 +5451,12 @@
       <c r="A110" s="53" t="s">
         <v>185</v>
       </c>
-      <c r="B110" s="195" t="s">
+      <c r="B110" s="116" t="s">
         <v>186</v>
       </c>
-      <c r="C110" s="195"/>
-      <c r="D110" s="195"/>
-      <c r="E110" s="195"/>
+      <c r="C110" s="116"/>
+      <c r="D110" s="116"/>
+      <c r="E110" s="116"/>
       <c r="F110" s="54" t="s">
         <v>64</v>
       </c>
@@ -5382,12 +5468,12 @@
       <c r="A111" s="52" t="s">
         <v>187</v>
       </c>
-      <c r="B111" s="191" t="s">
+      <c r="B111" s="112" t="s">
         <v>189</v>
       </c>
-      <c r="C111" s="191"/>
-      <c r="D111" s="191"/>
-      <c r="E111" s="191"/>
+      <c r="C111" s="112"/>
+      <c r="D111" s="112"/>
+      <c r="E111" s="112"/>
       <c r="F111" s="57" t="s">
         <v>193</v>
       </c>
@@ -5404,55 +5490,65 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="132">
-    <mergeCell ref="A78:A79"/>
-    <mergeCell ref="B78:B79"/>
-    <mergeCell ref="C78:E78"/>
-    <mergeCell ref="C79:E79"/>
-    <mergeCell ref="A80:B80"/>
-    <mergeCell ref="C80:E80"/>
-    <mergeCell ref="A81:A82"/>
-    <mergeCell ref="C81:E81"/>
-    <mergeCell ref="C82:D82"/>
-    <mergeCell ref="C57:E57"/>
-    <mergeCell ref="B111:E111"/>
-    <mergeCell ref="B108:E108"/>
-    <mergeCell ref="B103:E103"/>
-    <mergeCell ref="B104:E104"/>
-    <mergeCell ref="B105:E105"/>
-    <mergeCell ref="B106:E106"/>
-    <mergeCell ref="B107:E107"/>
-    <mergeCell ref="B109:E109"/>
-    <mergeCell ref="B110:E110"/>
-    <mergeCell ref="C93:E93"/>
-    <mergeCell ref="C94:E94"/>
-    <mergeCell ref="C95:E95"/>
-    <mergeCell ref="C98:E98"/>
-    <mergeCell ref="C99:E99"/>
-    <mergeCell ref="C96:E96"/>
-    <mergeCell ref="C97:E97"/>
-    <mergeCell ref="C70:E70"/>
-    <mergeCell ref="C71:E71"/>
-    <mergeCell ref="G38:G39"/>
-    <mergeCell ref="B40:B41"/>
-    <mergeCell ref="C40:E40"/>
-    <mergeCell ref="G40:G41"/>
-    <mergeCell ref="C61:E61"/>
-    <mergeCell ref="A43:A48"/>
-    <mergeCell ref="C45:E45"/>
-    <mergeCell ref="C46:E46"/>
-    <mergeCell ref="C42:E42"/>
-    <mergeCell ref="C44:E44"/>
-    <mergeCell ref="F38:F39"/>
-    <mergeCell ref="F40:F41"/>
-    <mergeCell ref="D41:E41"/>
-    <mergeCell ref="A49:B49"/>
-    <mergeCell ref="C49:E49"/>
-    <mergeCell ref="C47:E47"/>
-    <mergeCell ref="C48:E48"/>
-    <mergeCell ref="B52:B59"/>
-    <mergeCell ref="C58:E58"/>
-    <mergeCell ref="C56:E56"/>
+  <mergeCells count="131">
+    <mergeCell ref="C7:E7"/>
+    <mergeCell ref="B2:B7"/>
+    <mergeCell ref="A63:A64"/>
+    <mergeCell ref="D39:E39"/>
+    <mergeCell ref="C85:E85"/>
+    <mergeCell ref="C86:E86"/>
+    <mergeCell ref="C87:E87"/>
+    <mergeCell ref="C88:E88"/>
+    <mergeCell ref="C89:E89"/>
+    <mergeCell ref="C76:E76"/>
+    <mergeCell ref="A37:A42"/>
+    <mergeCell ref="C37:E37"/>
+    <mergeCell ref="B38:B39"/>
+    <mergeCell ref="C38:E38"/>
+    <mergeCell ref="C43:E43"/>
+    <mergeCell ref="A52:A60"/>
+    <mergeCell ref="C52:E52"/>
+    <mergeCell ref="C53:E53"/>
+    <mergeCell ref="C54:E54"/>
+    <mergeCell ref="C55:E55"/>
+    <mergeCell ref="C59:E59"/>
+    <mergeCell ref="C60:E60"/>
+    <mergeCell ref="C77:E77"/>
+    <mergeCell ref="C68:E68"/>
+    <mergeCell ref="A66:A71"/>
+    <mergeCell ref="C66:E66"/>
+    <mergeCell ref="B67:B68"/>
+    <mergeCell ref="C67:E67"/>
+    <mergeCell ref="C75:E75"/>
+    <mergeCell ref="C18:E18"/>
+    <mergeCell ref="C19:E19"/>
+    <mergeCell ref="C34:E34"/>
+    <mergeCell ref="B35:B36"/>
+    <mergeCell ref="C35:E35"/>
+    <mergeCell ref="C36:E36"/>
+    <mergeCell ref="C63:E63"/>
+    <mergeCell ref="C64:E64"/>
+    <mergeCell ref="C65:E65"/>
+    <mergeCell ref="B69:B70"/>
+    <mergeCell ref="C69:E69"/>
+    <mergeCell ref="A72:A77"/>
+    <mergeCell ref="C72:E72"/>
+    <mergeCell ref="C73:E73"/>
+    <mergeCell ref="B74:B75"/>
+    <mergeCell ref="C74:E74"/>
+    <mergeCell ref="B76:B77"/>
+    <mergeCell ref="C29:E29"/>
+    <mergeCell ref="C31:E31"/>
+    <mergeCell ref="A32:A36"/>
+    <mergeCell ref="C32:E32"/>
+    <mergeCell ref="C33:E33"/>
+    <mergeCell ref="C11:E11"/>
+    <mergeCell ref="C12:E12"/>
+    <mergeCell ref="C13:E13"/>
+    <mergeCell ref="C14:E14"/>
+    <mergeCell ref="C15:E15"/>
+    <mergeCell ref="C16:E16"/>
+    <mergeCell ref="C17:E17"/>
     <mergeCell ref="G26:G27"/>
     <mergeCell ref="F5:F6"/>
     <mergeCell ref="C20:E20"/>
@@ -5477,66 +5573,55 @@
     <mergeCell ref="C5:E5"/>
     <mergeCell ref="F26:F27"/>
     <mergeCell ref="C21:E21"/>
-    <mergeCell ref="C29:E29"/>
-    <mergeCell ref="C31:E31"/>
-    <mergeCell ref="A32:A36"/>
-    <mergeCell ref="C32:E32"/>
-    <mergeCell ref="C33:E33"/>
-    <mergeCell ref="C11:E11"/>
-    <mergeCell ref="C12:E12"/>
-    <mergeCell ref="C13:E13"/>
-    <mergeCell ref="C14:E14"/>
-    <mergeCell ref="C15:E15"/>
-    <mergeCell ref="C16:E16"/>
-    <mergeCell ref="C17:E17"/>
+    <mergeCell ref="G38:G39"/>
+    <mergeCell ref="B40:B41"/>
+    <mergeCell ref="C40:E40"/>
+    <mergeCell ref="G40:G41"/>
+    <mergeCell ref="C61:E61"/>
+    <mergeCell ref="A43:A48"/>
+    <mergeCell ref="C45:E45"/>
+    <mergeCell ref="C46:E46"/>
+    <mergeCell ref="C42:E42"/>
+    <mergeCell ref="C44:E44"/>
+    <mergeCell ref="F38:F39"/>
+    <mergeCell ref="F40:F41"/>
+    <mergeCell ref="D41:E41"/>
+    <mergeCell ref="A49:B49"/>
+    <mergeCell ref="C49:E49"/>
+    <mergeCell ref="C47:E47"/>
+    <mergeCell ref="C48:E48"/>
+    <mergeCell ref="B52:B59"/>
+    <mergeCell ref="C58:E58"/>
+    <mergeCell ref="C56:E56"/>
+    <mergeCell ref="C57:E57"/>
+    <mergeCell ref="B111:E111"/>
+    <mergeCell ref="B108:E108"/>
+    <mergeCell ref="B103:E103"/>
+    <mergeCell ref="B104:E104"/>
+    <mergeCell ref="B105:E105"/>
+    <mergeCell ref="B106:E106"/>
+    <mergeCell ref="B107:E107"/>
+    <mergeCell ref="B109:E109"/>
+    <mergeCell ref="B110:E110"/>
+    <mergeCell ref="C93:E93"/>
+    <mergeCell ref="C94:E94"/>
+    <mergeCell ref="C95:E95"/>
+    <mergeCell ref="C98:E98"/>
+    <mergeCell ref="C99:E99"/>
+    <mergeCell ref="C96:E96"/>
+    <mergeCell ref="C97:E97"/>
+    <mergeCell ref="C70:E70"/>
+    <mergeCell ref="C71:E71"/>
     <mergeCell ref="C90:E90"/>
     <mergeCell ref="C62:E62"/>
-    <mergeCell ref="A66:A71"/>
-    <mergeCell ref="C66:E66"/>
-    <mergeCell ref="B67:B68"/>
-    <mergeCell ref="C67:E67"/>
-    <mergeCell ref="C75:E75"/>
-    <mergeCell ref="C18:E18"/>
-    <mergeCell ref="C19:E19"/>
-    <mergeCell ref="C34:E34"/>
-    <mergeCell ref="B35:B36"/>
-    <mergeCell ref="C35:E35"/>
-    <mergeCell ref="C36:E36"/>
-    <mergeCell ref="C63:E63"/>
-    <mergeCell ref="C64:E64"/>
-    <mergeCell ref="C65:E65"/>
-    <mergeCell ref="B69:B70"/>
-    <mergeCell ref="C69:E69"/>
-    <mergeCell ref="A72:A77"/>
-    <mergeCell ref="C72:E72"/>
-    <mergeCell ref="C73:E73"/>
-    <mergeCell ref="B74:B75"/>
-    <mergeCell ref="C74:E74"/>
-    <mergeCell ref="B76:B77"/>
-    <mergeCell ref="C7:E7"/>
-    <mergeCell ref="B2:B7"/>
-    <mergeCell ref="A63:A64"/>
-    <mergeCell ref="D39:E39"/>
-    <mergeCell ref="C85:E85"/>
-    <mergeCell ref="C86:E86"/>
-    <mergeCell ref="C87:E87"/>
-    <mergeCell ref="C88:E88"/>
-    <mergeCell ref="C89:E89"/>
-    <mergeCell ref="C76:E76"/>
-    <mergeCell ref="A37:A42"/>
-    <mergeCell ref="C37:E37"/>
-    <mergeCell ref="B38:B39"/>
-    <mergeCell ref="C38:E38"/>
-    <mergeCell ref="C43:E43"/>
-    <mergeCell ref="A52:A60"/>
-    <mergeCell ref="C52:E52"/>
-    <mergeCell ref="C53:E53"/>
-    <mergeCell ref="C54:E54"/>
-    <mergeCell ref="C55:E55"/>
-    <mergeCell ref="C59:E59"/>
-    <mergeCell ref="C60:E60"/>
-    <mergeCell ref="C77:E77"/>
-    <mergeCell ref="C68:E68"/>
+    <mergeCell ref="A78:A79"/>
+    <mergeCell ref="B78:B79"/>
+    <mergeCell ref="C78:E78"/>
+    <mergeCell ref="C79:E79"/>
+    <mergeCell ref="C80:E80"/>
+    <mergeCell ref="A81:A82"/>
+    <mergeCell ref="C81:E81"/>
+    <mergeCell ref="C82:D82"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <printOptions horizontalCentered="1"/>
